--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet name="Roadmap" sheetId="1" r:id="rId1"/>
     <sheet name="How to use" sheetId="2" r:id="rId2"/>
-    <sheet name="People" sheetId="3" r:id="rId3"/>
+    <sheet name="Questions" sheetId="3" r:id="rId3"/>
+    <sheet name="People" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -488,7 +489,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>1 open of 1</v>
       </c>
     </row>
     <row r="3">
@@ -3540,7 +3541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
@@ -3572,27 +3573,98 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Topic is the identity of a row. Renaming one restarts its progress.</v>
+        <v>The Questions sheet holds one row per message: a Question row, then its Comment rows, grouped by Topic and Thread.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Commit this file over the old one in the repository to publish progress.</v>
+        <v>Topic is the identity of a row. Renaming one restarts its progress.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Commit this file over the old one in the repository to publish progress.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>Do not put organization IDs, source IDs, endpoints, key names or key values in this file.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <cols>
+    <col min="1" max="1" width="44.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Topic</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Thread</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Kind</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Text</v>
+      </c>
+      <c r="E1" t="str">
+        <v>By</v>
+      </c>
+      <c r="F1" t="str">
+        <v>On</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>What Coveo is and where it fits in our stack</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Question</v>
+      </c>
+      <c r="D2" t="str">
+        <v>what</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Divyashree</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Sep 15</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Open</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B3"/>
   <cols>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -3600,7 +3600,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -3657,9 +3657,32 @@
         <v>Open</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>What Coveo is and where it fits in our stack</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Comment</v>
+      </c>
+      <c r="D3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Akshay</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Sep 15</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>1 open of 1</v>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -3600,7 +3600,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -3634,55 +3634,9 @@
         <v>Status</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>What Coveo is and where it fits in our stack</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Question</v>
-      </c>
-      <c r="D2" t="str">
-        <v>what</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Divyashree</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Sep 15</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Open</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>What Coveo is and where it fits in our stack</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Comment</v>
-      </c>
-      <c r="D3" t="str">
-        <v>yes</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Akshay</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Sep 15</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -475,7 +475,7 @@
         <v>docs.coveo.com - search: Coveo Platform overview</v>
       </c>
       <c r="G2" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L81"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -653,19 +653,19 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>Prod and non-prod pairing for each licence</v>
+        <v>What each licence limits in practice</v>
       </c>
       <c r="D7" t="str">
-        <v>Which non-prod organization belongs to which prod organization, naming convention, and how access is requested for each.</v>
+        <v>Index size, source count, query volume, number of ML models. Where to read current consumption in the console.</v>
       </c>
       <c r="E7" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F7" t="str">
-        <v>Internal - environment matrix</v>
+        <v>docs.coveo.com - search: licence limits</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>Contractual figures come from the contract, not from the docs.</v>
       </c>
       <c r="H7" t="str">
         <v>No</v>
@@ -685,25 +685,25 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>1. Coveo Platform overview</v>
+        <v>2. Platform foundation and the Admin Console</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Find anything in the Administration Console without help, and know what each tab changes.</v>
       </c>
       <c r="C8" t="str">
-        <v>What each licence limits in practice</v>
+        <v>Moving configuration between organizations</v>
       </c>
       <c r="D8" t="str">
-        <v>Index size, source count, query volume, number of ML models. Where to read current consumption in the console.</v>
+        <v>What is configured per organization, what we keep identical across prod and non-prod, and how a change is promoted.</v>
       </c>
       <c r="E8" t="str">
         <v>Concept</v>
       </c>
       <c r="F8" t="str">
-        <v>docs.coveo.com - search: licence limits</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G8" t="str">
-        <v>Contractual figures come from the contract, not from the docs.</v>
+        <v/>
       </c>
       <c r="H8" t="str">
         <v>No</v>
@@ -726,19 +726,19 @@
         <v>2. Platform foundation and the Admin Console</v>
       </c>
       <c r="B9" t="str">
-        <v>Find anything in the Administration Console without help, and know what each tab changes.</v>
+        <v/>
       </c>
       <c r="C9" t="str">
-        <v>Moving configuration between organizations</v>
+        <v>Content tab: sources and Content Browser</v>
       </c>
       <c r="D9" t="str">
-        <v>What is configured per organization, what we keep identical across prod and non-prod, and how a change is promoted.</v>
+        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
       </c>
       <c r="E9" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F9" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -767,16 +767,16 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>Content tab: sources and Content Browser</v>
+        <v>Content tab: fields and mappings</v>
       </c>
       <c r="D10" t="str">
-        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
+        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
       </c>
       <c r="E10" t="str">
         <v>Demo</v>
       </c>
       <c r="F10" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>docs.coveo.com - search: fields</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -805,16 +805,16 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>Content tab: fields and mappings</v>
+        <v>Content tab: security identities and providers</v>
       </c>
       <c r="D11" t="str">
-        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
+        <v>Which of our content is secured, which is public, and how identities reach the index.</v>
       </c>
       <c r="E11" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F11" t="str">
-        <v>docs.coveo.com - search: fields</v>
+        <v>docs.coveo.com - search: security identities</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -843,16 +843,16 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Content tab: security identities and providers</v>
+        <v>Search Optimization tab: query pipelines and statements</v>
       </c>
       <c r="D12" t="str">
-        <v>Which of our content is secured, which is public, and how identities reach the index.</v>
+        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
       </c>
       <c r="E12" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: security identities</v>
+        <v>docs.coveo.com - search: query pipelines</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -881,16 +881,16 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Search Optimization tab: query pipelines and statements</v>
+        <v>Machine Learning tab</v>
       </c>
       <c r="D13" t="str">
-        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
+        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
       </c>
       <c r="E13" t="str">
         <v>Demo</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: query pipelines</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -919,16 +919,16 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Machine Learning tab</v>
+        <v>Analytics tab: dashboards, reports and visit inspection</v>
       </c>
       <c r="D14" t="str">
-        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
+        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
       </c>
       <c r="E14" t="str">
         <v>Demo</v>
       </c>
       <c r="F14" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning</v>
+        <v>docs.coveo.com - search: usage analytics dashboards</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -957,16 +957,16 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Analytics tab: dashboards, reports and visit inspection</v>
+        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
       </c>
       <c r="D15" t="str">
-        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
+        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
       </c>
       <c r="E15" t="str">
         <v>Demo</v>
       </c>
       <c r="F15" t="str">
-        <v>docs.coveo.com - search: usage analytics dashboards</v>
+        <v>docs.coveo.com - search: catalog product listing</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -995,19 +995,19 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
+        <v>Organization tab: members, groups and API keys</v>
       </c>
       <c r="D16" t="str">
-        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
+        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
       </c>
       <c r="E16" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F16" t="str">
-        <v>docs.coveo.com - search: catalog product listing</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>Never share key values. Grant through groups.</v>
       </c>
       <c r="H16" t="str">
         <v>No</v>
@@ -1033,19 +1033,19 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Organization tab: members, groups and API keys</v>
+        <v>Organization tab: settings, licence and consumption</v>
       </c>
       <c r="D17" t="str">
-        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
+        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E17" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F17" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>docs.coveo.com - search: organization settings</v>
       </c>
       <c r="G17" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H17" t="str">
         <v>No</v>
@@ -1071,16 +1071,16 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>Organization tab: settings, licence and consumption</v>
+        <v>Quotas, limits and what happens at the ceiling</v>
       </c>
       <c r="D18" t="str">
-        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
+        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
       </c>
       <c r="E18" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F18" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v>docs.coveo.com - search: platform limits</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1109,16 +1109,16 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Quotas, limits and what happens at the ceiling</v>
+        <v>Who owns what, and what needs approval</v>
       </c>
       <c r="D19" t="str">
-        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
+        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
       </c>
       <c r="E19" t="str">
         <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v>docs.coveo.com - search: platform limits</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1141,22 +1141,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2. Platform foundation and the Admin Console</v>
+        <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C20" t="str">
-        <v>Who owns what, and what needs approval</v>
+        <v>Which console configuration the JAR depends on</v>
       </c>
       <c r="D20" t="str">
-        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
+        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
       </c>
       <c r="E20" t="str">
         <v>Concept</v>
       </c>
       <c r="F20" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: push source</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1182,19 +1182,19 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B21" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C21" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D21" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E21" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F21" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1223,19 +1223,19 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>Where credentials live and how they rotate</v>
       </c>
       <c r="D22" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
       </c>
       <c r="E22" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F22" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
       </c>
       <c r="H22" t="str">
         <v>No</v>
@@ -1261,19 +1261,19 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D23" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E23" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F23" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G23" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H23" t="str">
         <v>No</v>
@@ -1299,10 +1299,10 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D24" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E24" t="str">
         <v>Code walkthrough</v>
@@ -1337,16 +1337,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D25" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E25" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1375,16 +1375,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>Prove the wiring on non-prod before prod</v>
       </c>
       <c r="D26" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
       </c>
       <c r="E26" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F26" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1407,22 +1407,22 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B27" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C27" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D27" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E27" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1448,19 +1448,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B28" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C28" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D28" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E28" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F28" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1489,16 +1489,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D29" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E29" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F29" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1527,16 +1527,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D30" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E30" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1565,16 +1565,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D31" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E31" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1603,16 +1603,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D32" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E32" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1641,16 +1641,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D33" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E33" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F33" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1679,19 +1679,19 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D34" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E34" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H34" t="str">
         <v>No</v>
@@ -1711,25 +1711,25 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C35" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D35" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E35" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G35" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H35" t="str">
         <v>No</v>
@@ -1752,19 +1752,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B36" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D36" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E36" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1793,16 +1793,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D37" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E37" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1831,16 +1831,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D38" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E38" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1869,16 +1869,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D39" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E39" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1907,16 +1907,16 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D40" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E40" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1939,22 +1939,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C41" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D41" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E41" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1980,19 +1980,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B42" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C42" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D42" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E42" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F42" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2021,16 +2021,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D43" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E43" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F43" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2059,16 +2059,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D44" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E44" t="str">
         <v>Concept</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2097,16 +2097,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D45" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E45" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2135,10 +2135,10 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D46" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E46" t="str">
         <v>Hands-on</v>
@@ -2173,16 +2173,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D47" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E47" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C48" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D48" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E48" t="str">
         <v>Concept</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2246,19 +2246,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B49" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D49" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E49" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2287,19 +2287,19 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D50" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E50" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H50" t="str">
         <v>No</v>
@@ -2325,19 +2325,19 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D51" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E51" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F51" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G51" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>No</v>
@@ -2363,16 +2363,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D52" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E52" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F52" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2401,16 +2401,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D53" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E53" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F53" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2433,22 +2433,22 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C54" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D54" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E54" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F54" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2474,19 +2474,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B55" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C55" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D55" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E55" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2515,16 +2515,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D56" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E56" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2553,16 +2553,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D57" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E57" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2591,16 +2591,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D58" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2629,16 +2629,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D59" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E59" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2667,19 +2667,19 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D60" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E60" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H60" t="str">
         <v>No</v>
@@ -2699,25 +2699,25 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C61" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D61" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E61" t="str">
         <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G61" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H61" t="str">
         <v>No</v>
@@ -2740,19 +2740,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B62" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D62" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E62" t="str">
         <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2781,16 +2781,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D63" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E63" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2819,16 +2819,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D64" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E64" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2857,16 +2857,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D65" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E65" t="str">
         <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2895,16 +2895,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D66" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E66" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2933,16 +2933,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D67" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E67" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C68" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D68" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E68" t="str">
         <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3006,19 +3006,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B69" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D69" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E69" t="str">
         <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3047,16 +3047,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D70" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E70" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3085,16 +3085,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D71" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E71" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3123,16 +3123,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D72" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E72" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F72" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3161,16 +3161,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D73" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E73" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F73" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3199,16 +3199,16 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D74" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E74" t="str">
         <v>Concept</v>
       </c>
       <c r="F74" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3231,22 +3231,22 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C75" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D75" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E75" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F75" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3272,19 +3272,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B76" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C76" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D76" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E76" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F76" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3313,16 +3313,16 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D77" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E77" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F77" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3351,16 +3351,16 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D78" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E78" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F78" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3389,16 +3389,16 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D79" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E79" t="str">
         <v>Concept</v>
       </c>
       <c r="F79" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3427,16 +3427,16 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D80" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E80" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F80" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3465,19 +3465,19 @@
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D81" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E81" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F81" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G81" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H81" t="str">
         <v>No</v>
@@ -3492,50 +3492,12 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B82" t="str">
-        <v/>
-      </c>
-      <c r="C82" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D82" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E82" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F82" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G82" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H82" t="str">
-        <v>No</v>
-      </c>
-      <c r="I82" t="str">
-        <v/>
-      </c>
-      <c r="J82" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K82" t="str">
-        <v/>
-      </c>
-      <c r="L82" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -472,7 +472,7 @@
         <v>Concept</v>
       </c>
       <c r="F2" t="str">
-        <v>docs.coveo.com - search: Coveo Platform overview</v>
+        <v>https://docs.coveo.com/en/ladb6157/coveo-for-commerce/coveo-for-commerce-capabilities</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -3682,7 +3682,7 @@
         <v>Learning</v>
       </c>
       <c r="B3" t="str">
-        <v xml:space="preserve">DIVYASHREE </v>
+        <v>DIVYASHREE</v>
       </c>
     </row>
   </sheetData>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L80"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -501,19 +501,19 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>Organization model: production and non-production</v>
+        <v>Licence: RGG and RSW region licence</v>
       </c>
       <c r="D3" t="str">
-        <v>How many organizations we hold, how prod and non-prod are paired, and how we keep them in step.</v>
+        <v>What this licence covers, which regions and storefronts sit behind it, which organizations it maps to, and who owns renewal.</v>
       </c>
       <c r="E3" t="str">
         <v>Concept</v>
       </c>
       <c r="F3" t="str">
-        <v>docs.coveo.com - search: organization</v>
+        <v>Internal - licence register</v>
       </c>
       <c r="G3" t="str">
-        <v>Record org IDs in the private runbook, not in this file.</v>
+        <v>Confirm the full names and scope with the account owner before quoting them.</v>
       </c>
       <c r="H3" t="str">
         <v>No</v>
@@ -539,10 +539,10 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>Licence: RGG and RSW region licence</v>
+        <v>Licence: RSP licence</v>
       </c>
       <c r="D4" t="str">
-        <v>What this licence covers, which regions and storefronts sit behind it, which organizations it maps to, and who owns renewal.</v>
+        <v>Scope of the RSP licence, the organizations it maps to, and how it differs from the region licence.</v>
       </c>
       <c r="E4" t="str">
         <v>Concept</v>
@@ -551,7 +551,7 @@
         <v>Internal - licence register</v>
       </c>
       <c r="G4" t="str">
-        <v>Confirm the full names and scope with the account owner before quoting them.</v>
+        <v>Confirm scope with the account owner.</v>
       </c>
       <c r="H4" t="str">
         <v>No</v>
@@ -577,10 +577,10 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>Licence: RSP licence</v>
+        <v>Licence: RUI licence</v>
       </c>
       <c r="D5" t="str">
-        <v>Scope of the RSP licence, the organizations it maps to, and how it differs from the region licence.</v>
+        <v>Scope of the RUI licence, the organizations it maps to, and what it is used for.</v>
       </c>
       <c r="E5" t="str">
         <v>Concept</v>
@@ -615,19 +615,19 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>Licence: RUI licence</v>
+        <v>What each licence limits in practice</v>
       </c>
       <c r="D6" t="str">
-        <v>Scope of the RUI licence, the organizations it maps to, and what it is used for.</v>
+        <v>Index size, source count, query volume, number of ML models. Where to read current consumption in the console.</v>
       </c>
       <c r="E6" t="str">
         <v>Concept</v>
       </c>
       <c r="F6" t="str">
-        <v>Internal - licence register</v>
+        <v>docs.coveo.com - search: licence limits</v>
       </c>
       <c r="G6" t="str">
-        <v>Confirm scope with the account owner.</v>
+        <v>Contractual figures come from the contract, not from the docs.</v>
       </c>
       <c r="H6" t="str">
         <v>No</v>
@@ -647,25 +647,25 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>1. Coveo Platform overview</v>
+        <v>2. Platform foundation and the Admin Console</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Find anything in the Administration Console without help, and know what each tab changes.</v>
       </c>
       <c r="C7" t="str">
-        <v>What each licence limits in practice</v>
+        <v>Moving configuration between organizations</v>
       </c>
       <c r="D7" t="str">
-        <v>Index size, source count, query volume, number of ML models. Where to read current consumption in the console.</v>
+        <v>What is configured per organization, what we keep identical across prod and non-prod, and how a change is promoted.</v>
       </c>
       <c r="E7" t="str">
         <v>Concept</v>
       </c>
       <c r="F7" t="str">
-        <v>docs.coveo.com - search: licence limits</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G7" t="str">
-        <v>Contractual figures come from the contract, not from the docs.</v>
+        <v/>
       </c>
       <c r="H7" t="str">
         <v>No</v>
@@ -688,19 +688,19 @@
         <v>2. Platform foundation and the Admin Console</v>
       </c>
       <c r="B8" t="str">
-        <v>Find anything in the Administration Console without help, and know what each tab changes.</v>
+        <v/>
       </c>
       <c r="C8" t="str">
-        <v>Moving configuration between organizations</v>
+        <v>Content tab: sources and Content Browser</v>
       </c>
       <c r="D8" t="str">
-        <v>What is configured per organization, what we keep identical across prod and non-prod, and how a change is promoted.</v>
+        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
       </c>
       <c r="E8" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F8" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -729,16 +729,16 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>Content tab: sources and Content Browser</v>
+        <v>Content tab: fields and mappings</v>
       </c>
       <c r="D9" t="str">
-        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
+        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
       </c>
       <c r="E9" t="str">
         <v>Demo</v>
       </c>
       <c r="F9" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>docs.coveo.com - search: fields</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -767,16 +767,16 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>Content tab: fields and mappings</v>
+        <v>Content tab: security identities and providers</v>
       </c>
       <c r="D10" t="str">
-        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
+        <v>Which of our content is secured, which is public, and how identities reach the index.</v>
       </c>
       <c r="E10" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F10" t="str">
-        <v>docs.coveo.com - search: fields</v>
+        <v>docs.coveo.com - search: security identities</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -805,16 +805,16 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>Content tab: security identities and providers</v>
+        <v>Search Optimization tab: query pipelines and statements</v>
       </c>
       <c r="D11" t="str">
-        <v>Which of our content is secured, which is public, and how identities reach the index.</v>
+        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
       </c>
       <c r="E11" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F11" t="str">
-        <v>docs.coveo.com - search: security identities</v>
+        <v>docs.coveo.com - search: query pipelines</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -843,16 +843,16 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Search Optimization tab: query pipelines and statements</v>
+        <v>Machine Learning tab</v>
       </c>
       <c r="D12" t="str">
-        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
+        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
       </c>
       <c r="E12" t="str">
         <v>Demo</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: query pipelines</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -881,16 +881,16 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Machine Learning tab</v>
+        <v>Analytics tab: dashboards, reports and visit inspection</v>
       </c>
       <c r="D13" t="str">
-        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
+        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
       </c>
       <c r="E13" t="str">
         <v>Demo</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning</v>
+        <v>docs.coveo.com - search: usage analytics dashboards</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -919,16 +919,16 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Analytics tab: dashboards, reports and visit inspection</v>
+        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
       </c>
       <c r="D14" t="str">
-        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
+        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
       </c>
       <c r="E14" t="str">
         <v>Demo</v>
       </c>
       <c r="F14" t="str">
-        <v>docs.coveo.com - search: usage analytics dashboards</v>
+        <v>docs.coveo.com - search: catalog product listing</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -957,19 +957,19 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
+        <v>Organization tab: members, groups and API keys</v>
       </c>
       <c r="D15" t="str">
-        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
+        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
       </c>
       <c r="E15" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F15" t="str">
-        <v>docs.coveo.com - search: catalog product listing</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>Never share key values. Grant through groups.</v>
       </c>
       <c r="H15" t="str">
         <v>No</v>
@@ -995,19 +995,19 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Organization tab: members, groups and API keys</v>
+        <v>Organization tab: settings, licence and consumption</v>
       </c>
       <c r="D16" t="str">
-        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
+        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E16" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F16" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>docs.coveo.com - search: organization settings</v>
       </c>
       <c r="G16" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H16" t="str">
         <v>No</v>
@@ -1033,16 +1033,16 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Organization tab: settings, licence and consumption</v>
+        <v>Quotas, limits and what happens at the ceiling</v>
       </c>
       <c r="D17" t="str">
-        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
+        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
       </c>
       <c r="E17" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F17" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v>docs.coveo.com - search: platform limits</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1071,16 +1071,16 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>Quotas, limits and what happens at the ceiling</v>
+        <v>Who owns what, and what needs approval</v>
       </c>
       <c r="D18" t="str">
-        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
+        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
       </c>
       <c r="E18" t="str">
         <v>Concept</v>
       </c>
       <c r="F18" t="str">
-        <v>docs.coveo.com - search: platform limits</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1103,22 +1103,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2. Platform foundation and the Admin Console</v>
+        <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C19" t="str">
-        <v>Who owns what, and what needs approval</v>
+        <v>Which console configuration the JAR depends on</v>
       </c>
       <c r="D19" t="str">
-        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
+        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
       </c>
       <c r="E19" t="str">
         <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: push source</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1144,19 +1144,19 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B20" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D20" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E20" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F20" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1185,19 +1185,19 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>Where credentials live and how they rotate</v>
       </c>
       <c r="D21" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
       </c>
       <c r="E21" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F21" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
       </c>
       <c r="H21" t="str">
         <v>No</v>
@@ -1223,19 +1223,19 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D22" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E22" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F22" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G22" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H22" t="str">
         <v>No</v>
@@ -1261,10 +1261,10 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D23" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E23" t="str">
         <v>Code walkthrough</v>
@@ -1299,16 +1299,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D24" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E24" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F24" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1337,16 +1337,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>Prove the wiring on non-prod before prod</v>
       </c>
       <c r="D25" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
       </c>
       <c r="E25" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F25" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1369,22 +1369,22 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C26" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D26" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E26" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1410,19 +1410,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B27" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C27" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D27" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E27" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1451,16 +1451,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D28" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E28" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F28" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1489,16 +1489,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D29" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E29" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1527,16 +1527,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D30" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E30" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1565,16 +1565,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D31" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E31" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1603,16 +1603,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D32" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E32" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F32" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1641,19 +1641,19 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D33" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E33" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H33" t="str">
         <v>No</v>
@@ -1673,25 +1673,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C34" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D34" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E34" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G34" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H34" t="str">
         <v>No</v>
@@ -1714,19 +1714,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B35" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D35" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E35" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1755,16 +1755,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D36" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E36" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1793,16 +1793,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D37" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E37" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1831,16 +1831,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D38" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E38" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1869,16 +1869,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D39" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E39" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C40" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D40" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E40" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1942,19 +1942,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B41" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D41" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E41" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1983,16 +1983,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D42" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E42" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F42" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2021,16 +2021,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D43" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E43" t="str">
         <v>Concept</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2059,16 +2059,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D44" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E44" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2097,10 +2097,10 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D45" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E45" t="str">
         <v>Hands-on</v>
@@ -2135,16 +2135,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D46" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E46" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2167,22 +2167,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C47" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D47" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E47" t="str">
         <v>Concept</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2208,19 +2208,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B48" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C48" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D48" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E48" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2249,19 +2249,19 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D49" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E49" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H49" t="str">
         <v>No</v>
@@ -2287,19 +2287,19 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D50" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E50" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G50" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v>No</v>
@@ -2325,16 +2325,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D51" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E51" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F51" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2363,16 +2363,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D52" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E52" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F52" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2395,22 +2395,22 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C53" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D53" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E53" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F53" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2436,19 +2436,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B54" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C54" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D54" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E54" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2477,16 +2477,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D55" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E55" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2515,16 +2515,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D56" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E56" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2553,16 +2553,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D57" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E57" t="str">
         <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2591,16 +2591,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D58" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E58" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2629,19 +2629,19 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D59" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E59" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H59" t="str">
         <v>No</v>
@@ -2661,25 +2661,25 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C60" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D60" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G60" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H60" t="str">
         <v>No</v>
@@ -2702,19 +2702,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B61" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D61" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E61" t="str">
         <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2743,16 +2743,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D62" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E62" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2781,16 +2781,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D63" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E63" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2819,16 +2819,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D64" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E64" t="str">
         <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2857,16 +2857,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D65" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E65" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2895,16 +2895,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D66" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E66" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2927,22 +2927,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C67" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D67" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E67" t="str">
         <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2968,19 +2968,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B68" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D68" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E68" t="str">
         <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3009,16 +3009,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D69" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E69" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3047,16 +3047,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D70" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E70" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3085,16 +3085,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D71" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E71" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3123,16 +3123,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D72" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E72" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F72" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3161,16 +3161,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D73" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E73" t="str">
         <v>Concept</v>
       </c>
       <c r="F73" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3193,22 +3193,22 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C74" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D74" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E74" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F74" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3234,19 +3234,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B75" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C75" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D75" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E75" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F75" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3275,16 +3275,16 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D76" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E76" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F76" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3313,16 +3313,16 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D77" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E77" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F77" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3351,16 +3351,16 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D78" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E78" t="str">
         <v>Concept</v>
       </c>
       <c r="F78" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3389,16 +3389,16 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D79" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E79" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F79" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3427,19 +3427,19 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D80" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E80" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F80" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G80" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H80" t="str">
         <v>No</v>
@@ -3454,50 +3454,12 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B81" t="str">
-        <v/>
-      </c>
-      <c r="C81" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D81" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E81" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F81" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G81" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H81" t="str">
-        <v>No</v>
-      </c>
-      <c r="I81" t="str">
-        <v/>
-      </c>
-      <c r="J81" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K81" t="str">
-        <v/>
-      </c>
-      <c r="L81" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L80"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -510,7 +510,7 @@
         <v>Concept</v>
       </c>
       <c r="F3" t="str">
-        <v>Internal - licence register</v>
+        <v>https://platform-eu.cloud.coveo.com/admin/#/lindeagnonproduction1j1x9l0cn/home      https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home</v>
       </c>
       <c r="G3" t="str">
         <v>Confirm the full names and scope with the account owner before quoting them.</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -493,7 +493,7 @@
         <v/>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>1. Coveo Platform overview</v>
       </c>
@@ -507,13 +507,14 @@
         <v>What this licence covers, which regions and storefronts sit behind it, which organizations it maps to, and who owns renewal.</v>
       </c>
       <c r="E3" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F3" t="str">
-        <v>https://platform-eu.cloud.coveo.com/admin/#/lindeagnonproduction1j1x9l0cn/home      https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Confirm the full names and scope with the account owner before quoting them.</v>
+        <v>Organization Liks</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Non - prod -- https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home
+Production :  https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home</v>
       </c>
       <c r="H3" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -513,8 +513,9 @@
         <v>Organization Liks</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Non - prod -- https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home
-Production :  https://platform-eu.cloud.coveo.com/admin/#/lindeagproduction1zc59nqc/home</v>
+        <v xml:space="preserve">Non - prod -lindeagproduction1zc59nqc
+\n
+Production : lindeagproduction1zc59nqc</v>
       </c>
       <c r="H3" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -514,7 +514,6 @@
       </c>
       <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">Non - prod -lindeagproduction1zc59nqc
-\n
 Production : lindeagproduction1zc59nqc</v>
       </c>
       <c r="H3" t="str">

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -513,7 +513,7 @@
         <v>Organization Liks</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Non - prod -lindeagproduction1zc59nqc
+        <v xml:space="preserve">Non-prod:  lindeagproduction1zc59nqc
 Production : lindeagproduction1zc59nqc</v>
       </c>
       <c r="H3" t="str">

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -510,7 +510,7 @@
         <v>Hands-on</v>
       </c>
       <c r="F3" t="str">
-        <v>Organization Liks</v>
+        <v>Organization Id's</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
         <v xml:space="preserve">Non-prod:  lindeagproduction1zc59nqc

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -532,7 +532,7 @@
         <v/>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>1. Coveo Platform overview</v>
       </c>
@@ -549,10 +549,11 @@
         <v>Concept</v>
       </c>
       <c r="F4" t="str">
-        <v>Internal - licence register</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Confirm scope with the account owner.</v>
+        <v>Organization Id's</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Non-Prod : bocaustralianonproduction352axqxp4
+Prod  : bocaustraliaproduction3dmakracm</v>
       </c>
       <c r="H4" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -585,10 +585,10 @@
         <v>Scope of the RUI licence, the organizations it maps to, and what it is used for.</v>
       </c>
       <c r="E5" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F5" t="str">
-        <v>Internal - licence register</v>
+        <v>Organization Id's</v>
       </c>
       <c r="G5" t="str">
         <v>Confirm scope with the account owner.</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -571,7 +571,7 @@
         <v/>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>1. Coveo Platform overview</v>
       </c>
@@ -590,8 +590,9 @@
       <c r="F5" t="str">
         <v>Organization Id's</v>
       </c>
-      <c r="G5" t="str">
-        <v>Confirm scope with the account owner.</v>
+      <c r="G5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Non-Prod : lindeagnonproduction6jocwb7an
+Production : lindeagproduction2wmje5cia</v>
       </c>
       <c r="H5" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -627,10 +627,10 @@
         <v>Concept</v>
       </c>
       <c r="F6" t="str">
-        <v>docs.coveo.com - search: licence limits</v>
+        <v>https://platform-eu.cloud.coveo.com/admin/#/lindeagnonproduction1j1x9l0cn/organization/license-and-usage/overview</v>
       </c>
       <c r="G6" t="str">
-        <v>Contractual figures come from the contract, not from the docs.</v>
+        <v>added link on RGG for example</v>
       </c>
       <c r="H6" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L79"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -770,16 +770,16 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>Content tab: security identities and providers</v>
+        <v>Search Optimization tab: query pipelines and statements</v>
       </c>
       <c r="D10" t="str">
-        <v>Which of our content is secured, which is public, and how identities reach the index.</v>
+        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
       </c>
       <c r="E10" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F10" t="str">
-        <v>docs.coveo.com - search: security identities</v>
+        <v>docs.coveo.com - search: query pipelines</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -808,16 +808,16 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>Search Optimization tab: query pipelines and statements</v>
+        <v>Machine Learning tab</v>
       </c>
       <c r="D11" t="str">
-        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
+        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
       </c>
       <c r="E11" t="str">
         <v>Demo</v>
       </c>
       <c r="F11" t="str">
-        <v>docs.coveo.com - search: query pipelines</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -846,16 +846,16 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Machine Learning tab</v>
+        <v>Analytics tab: dashboards, reports and visit inspection</v>
       </c>
       <c r="D12" t="str">
-        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
+        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
       </c>
       <c r="E12" t="str">
         <v>Demo</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning</v>
+        <v>docs.coveo.com - search: usage analytics dashboards</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -884,16 +884,16 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Analytics tab: dashboards, reports and visit inspection</v>
+        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
       </c>
       <c r="D13" t="str">
-        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
+        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
       </c>
       <c r="E13" t="str">
         <v>Demo</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: usage analytics dashboards</v>
+        <v>docs.coveo.com - search: catalog product listing</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -922,19 +922,19 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
+        <v>Organization tab: members, groups and API keys</v>
       </c>
       <c r="D14" t="str">
-        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
+        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
       </c>
       <c r="E14" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F14" t="str">
-        <v>docs.coveo.com - search: catalog product listing</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>Never share key values. Grant through groups.</v>
       </c>
       <c r="H14" t="str">
         <v>No</v>
@@ -960,19 +960,19 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Organization tab: members, groups and API keys</v>
+        <v>Organization tab: settings, licence and consumption</v>
       </c>
       <c r="D15" t="str">
-        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
+        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E15" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F15" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>docs.coveo.com - search: organization settings</v>
       </c>
       <c r="G15" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H15" t="str">
         <v>No</v>
@@ -998,16 +998,16 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Organization tab: settings, licence and consumption</v>
+        <v>Quotas, limits and what happens at the ceiling</v>
       </c>
       <c r="D16" t="str">
-        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
+        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
       </c>
       <c r="E16" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F16" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v>docs.coveo.com - search: platform limits</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1036,16 +1036,16 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>Quotas, limits and what happens at the ceiling</v>
+        <v>Who owns what, and what needs approval</v>
       </c>
       <c r="D17" t="str">
-        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
+        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
       </c>
       <c r="E17" t="str">
         <v>Concept</v>
       </c>
       <c r="F17" t="str">
-        <v>docs.coveo.com - search: platform limits</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1068,22 +1068,22 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2. Platform foundation and the Admin Console</v>
+        <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C18" t="str">
-        <v>Who owns what, and what needs approval</v>
+        <v>Which console configuration the JAR depends on</v>
       </c>
       <c r="D18" t="str">
-        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
+        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
       </c>
       <c r="E18" t="str">
         <v>Concept</v>
       </c>
       <c r="F18" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: push source</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1109,19 +1109,19 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B19" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C19" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D19" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E19" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F19" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1150,19 +1150,19 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>Where credentials live and how they rotate</v>
       </c>
       <c r="D20" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
       </c>
       <c r="E20" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F20" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
       </c>
       <c r="H20" t="str">
         <v>No</v>
@@ -1188,19 +1188,19 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D21" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E21" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F21" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G21" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H21" t="str">
         <v>No</v>
@@ -1226,10 +1226,10 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D22" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E22" t="str">
         <v>Code walkthrough</v>
@@ -1264,16 +1264,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D23" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E23" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F23" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1302,16 +1302,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>Prove the wiring on non-prod before prod</v>
       </c>
       <c r="D24" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
       </c>
       <c r="E24" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F24" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1334,22 +1334,22 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C25" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D25" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E25" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1375,19 +1375,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B26" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D26" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E26" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1416,16 +1416,16 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D27" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E27" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1454,16 +1454,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D28" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E28" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1492,16 +1492,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D29" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E29" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1530,16 +1530,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D30" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E30" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1568,16 +1568,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D31" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E31" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F31" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1606,19 +1606,19 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D32" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E32" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G32" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H32" t="str">
         <v>No</v>
@@ -1638,25 +1638,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C33" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D33" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E33" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G33" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H33" t="str">
         <v>No</v>
@@ -1679,19 +1679,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B34" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C34" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D34" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E34" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1720,16 +1720,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D35" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E35" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1758,16 +1758,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D36" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E36" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1796,16 +1796,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D37" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E37" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1834,16 +1834,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D38" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E38" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1866,22 +1866,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C39" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D39" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E39" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1907,19 +1907,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B40" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D40" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E40" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1948,16 +1948,16 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D41" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E41" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1986,16 +1986,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D42" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E42" t="str">
         <v>Concept</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2024,16 +2024,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D43" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E43" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2062,10 +2062,10 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D44" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E44" t="str">
         <v>Hands-on</v>
@@ -2100,16 +2100,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D45" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E45" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2132,22 +2132,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C46" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D46" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E46" t="str">
         <v>Concept</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2173,19 +2173,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B47" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D47" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E47" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2214,19 +2214,19 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D48" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E48" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G48" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H48" t="str">
         <v>No</v>
@@ -2252,19 +2252,19 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D49" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E49" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G49" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>No</v>
@@ -2290,16 +2290,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D50" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E50" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F50" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2328,16 +2328,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D51" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E51" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F51" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C52" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D52" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E52" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F52" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2401,19 +2401,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B53" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D53" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E53" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2442,16 +2442,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D54" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E54" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2480,16 +2480,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D55" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E55" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2518,16 +2518,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D56" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E56" t="str">
         <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2556,16 +2556,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D57" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E57" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2594,19 +2594,19 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D58" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E58" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G58" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H58" t="str">
         <v>No</v>
@@ -2626,25 +2626,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C59" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D59" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E59" t="str">
         <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G59" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H59" t="str">
         <v>No</v>
@@ -2667,19 +2667,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B60" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D60" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2708,16 +2708,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D61" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E61" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2746,16 +2746,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D62" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E62" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2784,16 +2784,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D63" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E63" t="str">
         <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2822,16 +2822,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D64" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E64" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2860,16 +2860,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D65" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E65" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C66" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D66" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E66" t="str">
         <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2933,19 +2933,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B67" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D67" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E67" t="str">
         <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2974,16 +2974,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D68" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E68" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3012,16 +3012,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D69" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E69" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3050,16 +3050,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D70" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E70" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3088,16 +3088,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D71" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E71" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3126,16 +3126,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D72" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E72" t="str">
         <v>Concept</v>
       </c>
       <c r="F72" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3158,22 +3158,22 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C73" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D73" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E73" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F73" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3199,19 +3199,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B74" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D74" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E74" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F74" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3240,16 +3240,16 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D75" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E75" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F75" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3278,16 +3278,16 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D76" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E76" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F76" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3316,16 +3316,16 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D77" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E77" t="str">
         <v>Concept</v>
       </c>
       <c r="F77" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3354,16 +3354,16 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D78" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E78" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F78" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3392,19 +3392,19 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D79" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E79" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F79" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G79" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H79" t="str">
         <v>No</v>
@@ -3419,50 +3419,12 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B80" t="str">
-        <v/>
-      </c>
-      <c r="C80" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D80" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E80" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F80" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G80" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H80" t="str">
-        <v>No</v>
-      </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
-      <c r="J80" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K80" t="str">
-        <v/>
-      </c>
-      <c r="L80" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L79"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L78"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -653,19 +653,19 @@
         <v>2. Platform foundation and the Admin Console</v>
       </c>
       <c r="B7" t="str">
-        <v>Find anything in the Administration Console without help, and know what each tab changes.</v>
+        <v/>
       </c>
       <c r="C7" t="str">
-        <v>Moving configuration between organizations</v>
+        <v>Content tab: sources and Content Browser</v>
       </c>
       <c r="D7" t="str">
-        <v>What is configured per organization, what we keep identical across prod and non-prod, and how a change is promoted.</v>
+        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
       </c>
       <c r="E7" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F7" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -694,16 +694,16 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>Content tab: sources and Content Browser</v>
+        <v>Content tab: fields and mappings</v>
       </c>
       <c r="D8" t="str">
-        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
+        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
       </c>
       <c r="E8" t="str">
         <v>Demo</v>
       </c>
       <c r="F8" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>docs.coveo.com - search: fields</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -732,16 +732,16 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>Content tab: fields and mappings</v>
+        <v>Search Optimization tab: query pipelines and statements</v>
       </c>
       <c r="D9" t="str">
-        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
+        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
       </c>
       <c r="E9" t="str">
         <v>Demo</v>
       </c>
       <c r="F9" t="str">
-        <v>docs.coveo.com - search: fields</v>
+        <v>docs.coveo.com - search: query pipelines</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -770,16 +770,16 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>Search Optimization tab: query pipelines and statements</v>
+        <v>Machine Learning tab</v>
       </c>
       <c r="D10" t="str">
-        <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
+        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
       </c>
       <c r="E10" t="str">
         <v>Demo</v>
       </c>
       <c r="F10" t="str">
-        <v>docs.coveo.com - search: query pipelines</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -808,16 +808,16 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>Machine Learning tab</v>
+        <v>Analytics tab: dashboards, reports and visit inspection</v>
       </c>
       <c r="D11" t="str">
-        <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
+        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
       </c>
       <c r="E11" t="str">
         <v>Demo</v>
       </c>
       <c r="F11" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning</v>
+        <v>docs.coveo.com - search: usage analytics dashboards</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -846,16 +846,16 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Analytics tab: dashboards, reports and visit inspection</v>
+        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
       </c>
       <c r="D12" t="str">
-        <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
+        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
       </c>
       <c r="E12" t="str">
         <v>Demo</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: usage analytics dashboards</v>
+        <v>docs.coveo.com - search: catalog product listing</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -884,19 +884,19 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
+        <v>Organization tab: members, groups and API keys</v>
       </c>
       <c r="D13" t="str">
-        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
+        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
       </c>
       <c r="E13" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: catalog product listing</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>Never share key values. Grant through groups.</v>
       </c>
       <c r="H13" t="str">
         <v>No</v>
@@ -922,19 +922,19 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Organization tab: members, groups and API keys</v>
+        <v>Organization tab: settings, licence and consumption</v>
       </c>
       <c r="D14" t="str">
-        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
+        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E14" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F14" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>docs.coveo.com - search: organization settings</v>
       </c>
       <c r="G14" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H14" t="str">
         <v>No</v>
@@ -960,16 +960,16 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Organization tab: settings, licence and consumption</v>
+        <v>Quotas, limits and what happens at the ceiling</v>
       </c>
       <c r="D15" t="str">
-        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
+        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
       </c>
       <c r="E15" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F15" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v>docs.coveo.com - search: platform limits</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -998,16 +998,16 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>Quotas, limits and what happens at the ceiling</v>
+        <v>Who owns what, and what needs approval</v>
       </c>
       <c r="D16" t="str">
-        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
+        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
       </c>
       <c r="E16" t="str">
         <v>Concept</v>
       </c>
       <c r="F16" t="str">
-        <v>docs.coveo.com - search: platform limits</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1030,22 +1030,22 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2. Platform foundation and the Admin Console</v>
+        <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C17" t="str">
-        <v>Who owns what, and what needs approval</v>
+        <v>Which console configuration the JAR depends on</v>
       </c>
       <c r="D17" t="str">
-        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
+        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
       </c>
       <c r="E17" t="str">
         <v>Concept</v>
       </c>
       <c r="F17" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: push source</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1071,19 +1071,19 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B18" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C18" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D18" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E18" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F18" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1112,19 +1112,19 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>Where credentials live and how they rotate</v>
       </c>
       <c r="D19" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
       </c>
       <c r="E19" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
       </c>
       <c r="H19" t="str">
         <v>No</v>
@@ -1150,19 +1150,19 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D20" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E20" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F20" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G20" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H20" t="str">
         <v>No</v>
@@ -1188,10 +1188,10 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D21" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E21" t="str">
         <v>Code walkthrough</v>
@@ -1226,16 +1226,16 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D22" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E22" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F22" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1264,16 +1264,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>Prove the wiring on non-prod before prod</v>
       </c>
       <c r="D23" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
       </c>
       <c r="E23" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F23" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1296,22 +1296,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C24" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D24" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E24" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F24" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1337,19 +1337,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B25" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C25" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D25" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E25" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1378,16 +1378,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D26" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E26" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1416,16 +1416,16 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D27" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E27" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F27" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1454,16 +1454,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D28" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E28" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1492,16 +1492,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D29" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E29" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1530,16 +1530,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D30" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E30" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F30" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1568,19 +1568,19 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D31" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E31" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G31" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H31" t="str">
         <v>No</v>
@@ -1600,25 +1600,25 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C32" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D32" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E32" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G32" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H32" t="str">
         <v>No</v>
@@ -1641,19 +1641,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B33" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D33" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E33" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1682,16 +1682,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D34" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E34" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1720,16 +1720,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D35" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E35" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1758,16 +1758,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D36" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E36" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1796,16 +1796,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D37" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E37" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1828,22 +1828,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C38" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D38" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E38" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1869,19 +1869,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D39" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E39" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1910,16 +1910,16 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D40" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E40" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1948,16 +1948,16 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D41" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E41" t="str">
         <v>Concept</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1986,16 +1986,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D42" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E42" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2024,10 +2024,10 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D43" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E43" t="str">
         <v>Hands-on</v>
@@ -2062,16 +2062,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D44" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E44" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2094,22 +2094,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C45" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D45" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E45" t="str">
         <v>Concept</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2135,19 +2135,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B46" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C46" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D46" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E46" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2176,19 +2176,19 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D47" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E47" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H47" t="str">
         <v>No</v>
@@ -2214,19 +2214,19 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D48" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E48" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G48" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H48" t="str">
         <v>No</v>
@@ -2252,16 +2252,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D49" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E49" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F49" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2290,16 +2290,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D50" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E50" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2322,22 +2322,22 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C51" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D51" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E51" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F51" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2363,19 +2363,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B52" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C52" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D52" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E52" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2404,16 +2404,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D53" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E53" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2442,16 +2442,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D54" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E54" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2480,16 +2480,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D55" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E55" t="str">
         <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2518,16 +2518,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D56" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E56" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2556,19 +2556,19 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D57" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E57" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G57" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H57" t="str">
         <v>No</v>
@@ -2588,25 +2588,25 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C58" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D58" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G58" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H58" t="str">
         <v>No</v>
@@ -2629,19 +2629,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B59" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D59" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E59" t="str">
         <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2670,16 +2670,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D60" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E60" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2708,16 +2708,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D61" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E61" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2746,16 +2746,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D62" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E62" t="str">
         <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2784,16 +2784,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D63" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E63" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2822,16 +2822,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D64" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E64" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2854,22 +2854,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C65" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D65" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E65" t="str">
         <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2895,19 +2895,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B66" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D66" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E66" t="str">
         <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2936,16 +2936,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D67" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E67" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2974,16 +2974,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D68" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E68" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3012,16 +3012,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D69" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E69" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3050,16 +3050,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D70" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E70" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3088,16 +3088,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D71" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E71" t="str">
         <v>Concept</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3120,22 +3120,22 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C72" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D72" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E72" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F72" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3161,19 +3161,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B73" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D73" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E73" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F73" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3202,16 +3202,16 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D74" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E74" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F74" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3240,16 +3240,16 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D75" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E75" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F75" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3278,16 +3278,16 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D76" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E76" t="str">
         <v>Concept</v>
       </c>
       <c r="F76" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3316,16 +3316,16 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D77" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E77" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F77" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3354,19 +3354,19 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D78" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E78" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F78" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G78" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H78" t="str">
         <v>No</v>
@@ -3381,50 +3381,12 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B79" t="str">
-        <v/>
-      </c>
-      <c r="C79" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D79" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E79" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F79" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G79" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H79" t="str">
-        <v>No</v>
-      </c>
-      <c r="I79" t="str">
-        <v/>
-      </c>
-      <c r="J79" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K79" t="str">
-        <v/>
-      </c>
-      <c r="L79" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L78"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -656,7 +656,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>Content tab: sources and Content Browser</v>
+        <v>Content tab: sources, Log Browser, Fields, Content Browser, Extentions</v>
       </c>
       <c r="D7" t="str">
         <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -662,10 +662,10 @@
         <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
       </c>
       <c r="E7" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F7" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v/>
       </c>
       <c r="G7" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -694,16 +694,16 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>Content tab: fields and mappings</v>
+        <v>Commerce tab: Catalog, StoreFront Assoctiation</v>
       </c>
       <c r="D8" t="str">
-        <v>Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F8" t="str">
-        <v>docs.coveo.com - search: fields</v>
+        <v/>
       </c>
       <c r="G8" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -648,7 +648,7 @@
         <v/>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>2. Platform foundation and the Admin Console</v>
       </c>
@@ -658,8 +658,9 @@
       <c r="C7" t="str">
         <v>Content tab: sources, Log Browser, Fields, Content Browser, Extentions</v>
       </c>
-      <c r="D7" t="str">
-        <v>Source list and status, adding and editing a source, inspecting an indexed item and its fields.</v>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Source list and status, adding and editing a source, inspecting an indexed item and its fields.
+Field list, field types, facet, sortable and free-text options, and where mappings are defined per source.</v>
       </c>
       <c r="E7" t="str">
         <v>Hands-on</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -733,16 +733,16 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>Search Optimization tab: query pipelines and statements</v>
+        <v>Search tab: Contitions and Query pipelines.</v>
       </c>
       <c r="D9" t="str">
         <v>Pipeline list, routing conditions, statement types, and which pipeline serves which storefront.</v>
       </c>
       <c r="E9" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F9" t="str">
-        <v>docs.coveo.com - search: query pipelines</v>
+        <v/>
       </c>
       <c r="G9" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -771,7 +771,7 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>Machine Learning tab</v>
+        <v>AI &amp; ML tab</v>
       </c>
       <c r="D10" t="str">
         <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -815,10 +815,10 @@
         <v>The dashboards we actually use, how to build a report, and how to open a single visit.</v>
       </c>
       <c r="E11" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F11" t="str">
-        <v>docs.coveo.com - search: usage analytics dashboards</v>
+        <v/>
       </c>
       <c r="G11" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -777,10 +777,10 @@
         <v>Model list, status, associations to pipelines, and what the model detail page tells you.</v>
       </c>
       <c r="E10" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F10" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning</v>
+        <v/>
       </c>
       <c r="G10" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L77"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -847,19 +847,19 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>Commerce tab: catalogs, product listings, Merchandising Hub</v>
+        <v>Organization tab: members, groups and API keys</v>
       </c>
       <c r="D12" t="str">
-        <v>How a catalog is configured, what a product listing is, and where merchandising rules live.</v>
+        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
       </c>
       <c r="E12" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: catalog product listing</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>Never share key values. Grant through groups.</v>
       </c>
       <c r="H12" t="str">
         <v>No</v>
@@ -885,19 +885,19 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>Organization tab: members, groups and API keys</v>
+        <v>Organization tab: settings, licence and consumption</v>
       </c>
       <c r="D13" t="str">
-        <v>Group privileges, creating and scoping an API key, and reading the activity log.</v>
+        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E13" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>docs.coveo.com - search: organization settings</v>
       </c>
       <c r="G13" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H13" t="str">
         <v>No</v>
@@ -923,16 +923,16 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>Organization tab: settings, licence and consumption</v>
+        <v>Quotas, limits and what happens at the ceiling</v>
       </c>
       <c r="D14" t="str">
-        <v>Organization settings we must not change casually, and where licence usage is reported.</v>
+        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
       </c>
       <c r="E14" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F14" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v>docs.coveo.com - search: platform limits</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -961,16 +961,16 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>Quotas, limits and what happens at the ceiling</v>
+        <v>Who owns what, and what needs approval</v>
       </c>
       <c r="D15" t="str">
-        <v>Index and query limits, payload and rate limits, and the symptoms when one is hit.</v>
+        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
       </c>
       <c r="E15" t="str">
         <v>Concept</v>
       </c>
       <c r="F15" t="str">
-        <v>docs.coveo.com - search: platform limits</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -993,22 +993,22 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2. Platform foundation and the Admin Console</v>
+        <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B16" t="str">
-        <v/>
+        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C16" t="str">
-        <v>Who owns what, and what needs approval</v>
+        <v>Which console configuration the JAR depends on</v>
       </c>
       <c r="D16" t="str">
-        <v>Which areas we change freely, which need a review, and which belong to the business.</v>
+        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
       </c>
       <c r="E16" t="str">
         <v>Concept</v>
       </c>
       <c r="F16" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: push source</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1034,19 +1034,19 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B17" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D17" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E17" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F17" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v>docs.coveo.com - search: API key privileges</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1075,19 +1075,19 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>Where credentials live and how they rotate</v>
       </c>
       <c r="D18" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
       </c>
       <c r="E18" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F18" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
       </c>
       <c r="H18" t="str">
         <v>No</v>
@@ -1113,19 +1113,19 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D19" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E19" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F19" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G19" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H19" t="str">
         <v>No</v>
@@ -1151,10 +1151,10 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D20" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E20" t="str">
         <v>Code walkthrough</v>
@@ -1189,16 +1189,16 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D21" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E21" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F21" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1227,16 +1227,16 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>Prove the wiring on non-prod before prod</v>
       </c>
       <c r="D22" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
       </c>
       <c r="E22" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F22" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1259,22 +1259,22 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C23" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D23" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E23" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F23" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1300,19 +1300,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B24" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D24" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E24" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F24" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D25" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E25" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1379,16 +1379,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D26" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E26" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F26" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1417,16 +1417,16 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D27" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E27" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F27" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1455,16 +1455,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D28" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E28" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1493,16 +1493,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D29" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E29" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F29" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1531,19 +1531,19 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D30" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E30" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F30" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H30" t="str">
         <v>No</v>
@@ -1563,25 +1563,25 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C31" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D31" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E31" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G31" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H31" t="str">
         <v>No</v>
@@ -1604,19 +1604,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B32" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C32" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D32" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E32" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1645,16 +1645,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D33" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E33" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D34" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E34" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D35" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E35" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1759,16 +1759,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D36" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E36" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1791,22 +1791,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C37" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D37" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E37" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B38" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D38" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E38" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,16 +1873,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D39" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E39" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1911,16 +1911,16 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D40" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E40" t="str">
         <v>Concept</v>
       </c>
       <c r="F40" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D41" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E41" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1987,10 +1987,10 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D42" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E42" t="str">
         <v>Hands-on</v>
@@ -2025,16 +2025,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D43" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E43" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2057,22 +2057,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C44" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D44" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E44" t="str">
         <v>Concept</v>
       </c>
       <c r="F44" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2098,19 +2098,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B45" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C45" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D45" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E45" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2139,19 +2139,19 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D46" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E46" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G46" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H46" t="str">
         <v>No</v>
@@ -2177,19 +2177,19 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D47" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E47" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G47" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H47" t="str">
         <v>No</v>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D48" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E48" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F48" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,16 +2253,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D49" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E49" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2285,22 +2285,22 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C50" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D50" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E50" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2326,19 +2326,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B51" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C51" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D51" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E51" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D52" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E52" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D53" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E53" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D54" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E54" t="str">
         <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,16 +2481,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D55" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E55" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,19 +2519,19 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D56" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E56" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G56" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H56" t="str">
         <v>No</v>
@@ -2551,25 +2551,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C57" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D57" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E57" t="str">
         <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G57" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H57" t="str">
         <v>No</v>
@@ -2592,19 +2592,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B58" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D58" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D59" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E59" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D60" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E60" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D61" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E61" t="str">
         <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D62" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E62" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D63" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E63" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2817,22 +2817,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C64" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D64" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E64" t="str">
         <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2858,19 +2858,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B65" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D65" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E65" t="str">
         <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D66" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E66" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D67" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E67" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D68" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E68" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D69" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E69" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D70" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E70" t="str">
         <v>Concept</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C71" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D71" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E71" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F71" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3124,19 +3124,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B72" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C72" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D72" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E72" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F72" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,16 +3165,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D73" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E73" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F73" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3203,16 +3203,16 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D74" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E74" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F74" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3241,16 +3241,16 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D75" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E75" t="str">
         <v>Concept</v>
       </c>
       <c r="F75" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3279,16 +3279,16 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D76" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E76" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F76" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3317,19 +3317,19 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D77" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E77" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F77" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G77" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H77" t="str">
         <v>No</v>
@@ -3344,50 +3344,12 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B78" t="str">
-        <v/>
-      </c>
-      <c r="C78" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D78" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E78" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F78" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G78" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H78" t="str">
-        <v>No</v>
-      </c>
-      <c r="I78" t="str">
-        <v/>
-      </c>
-      <c r="J78" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K78" t="str">
-        <v/>
-      </c>
-      <c r="L78" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L77"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -856,10 +856,10 @@
         <v>Hands-on</v>
       </c>
       <c r="F12" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>Never share key values. Grant through groups.</v>
+        <v/>
       </c>
       <c r="H12" t="str">
         <v>No</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -891,10 +891,10 @@
         <v>Organization settings we must not change casually, and where licence usage is reported.</v>
       </c>
       <c r="E13" t="str">
-        <v>Demo</v>
+        <v>Hands-on</v>
       </c>
       <c r="F13" t="str">
-        <v>docs.coveo.com - search: organization settings</v>
+        <v/>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -1008,7 +1008,7 @@
         <v>Concept</v>
       </c>
       <c r="F16" t="str">
-        <v>docs.coveo.com - search: push source</v>
+        <v/>
       </c>
       <c r="G16" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -1046,7 +1046,7 @@
         <v>Hands-on</v>
       </c>
       <c r="F17" t="str">
-        <v>docs.coveo.com - search: API key privileges</v>
+        <v/>
       </c>
       <c r="G17" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:L76"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1221,22 +1221,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B22" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C22" t="str">
-        <v>Prove the wiring on non-prod before prod</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D22" t="str">
-        <v>A dry run that confirms key, source and mapping are correct without touching production content.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E22" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F22" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1262,19 +1262,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B23" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C23" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D23" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E23" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F23" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1303,16 +1303,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D24" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E24" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F24" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D25" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E25" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F25" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1379,16 +1379,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D26" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E26" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F26" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1417,16 +1417,16 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D27" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E27" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F27" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1455,16 +1455,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D28" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E28" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F28" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1493,19 +1493,19 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D29" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E29" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F29" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G29" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H29" t="str">
         <v>No</v>
@@ -1525,25 +1525,25 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C30" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D30" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E30" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F30" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G30" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H30" t="str">
         <v>No</v>
@@ -1566,19 +1566,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B31" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D31" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E31" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1607,16 +1607,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D32" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E32" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1645,16 +1645,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D33" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E33" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D34" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E34" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D35" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E35" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C36" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D36" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E36" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1794,19 +1794,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B37" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D37" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E37" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1835,16 +1835,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D38" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E38" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,16 +1873,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D39" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E39" t="str">
         <v>Concept</v>
       </c>
       <c r="F39" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1911,16 +1911,16 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D40" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E40" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1949,10 +1949,10 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D41" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E41" t="str">
         <v>Hands-on</v>
@@ -1987,16 +1987,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D42" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E42" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2019,22 +2019,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C43" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D43" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E43" t="str">
         <v>Concept</v>
       </c>
       <c r="F43" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2060,19 +2060,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B44" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C44" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D44" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E44" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2101,19 +2101,19 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D45" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E45" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G45" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H45" t="str">
         <v>No</v>
@@ -2139,19 +2139,19 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D46" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E46" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G46" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H46" t="str">
         <v>No</v>
@@ -2177,16 +2177,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D47" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E47" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D48" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E48" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2247,22 +2247,22 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C49" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D49" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E49" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2288,19 +2288,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B50" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D50" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E50" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,16 +2329,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D51" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E51" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D52" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E52" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D53" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E53" t="str">
         <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D54" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E54" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,19 +2481,19 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D55" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E55" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G55" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H55" t="str">
         <v>No</v>
@@ -2513,25 +2513,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C56" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D56" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E56" t="str">
         <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G56" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H56" t="str">
         <v>No</v>
@@ -2554,19 +2554,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B57" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D57" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E57" t="str">
         <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D58" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E58" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D59" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E59" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D60" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D61" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E61" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D62" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E62" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C63" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D63" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E63" t="str">
         <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2820,19 +2820,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B64" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D64" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E64" t="str">
         <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D65" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E65" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D66" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E66" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D67" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E67" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D68" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E68" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D69" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E69" t="str">
         <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3045,22 +3045,22 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C70" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D70" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E70" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F70" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3086,19 +3086,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B71" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C71" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D71" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E71" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F71" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,16 +3127,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D72" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E72" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F72" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,16 +3165,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D73" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E73" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F73" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3203,16 +3203,16 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D74" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E74" t="str">
         <v>Concept</v>
       </c>
       <c r="F74" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3241,16 +3241,16 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D75" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E75" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F75" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3279,19 +3279,19 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D76" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E76" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F76" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G76" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H76" t="str">
         <v>No</v>
@@ -3306,50 +3306,12 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B77" t="str">
-        <v/>
-      </c>
-      <c r="C77" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D77" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E77" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F77" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G77" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H77" t="str">
-        <v>No</v>
-      </c>
-      <c r="I77" t="str">
-        <v/>
-      </c>
-      <c r="J77" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K77" t="str">
-        <v/>
-      </c>
-      <c r="L77" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L77"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L76"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -999,7 +999,7 @@
         <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
       </c>
       <c r="C16" t="str">
-        <v>Which console configuration the JAR depends on</v>
+        <v>Which Store configuration the JAR depends on</v>
       </c>
       <c r="D16" t="str">
         <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L75"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1075,19 +1075,19 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>Where credentials live and how they rotate</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D18" t="str">
-        <v>The secret store or pipeline variables we use, rotation process, and the check that no key sits in the repo.</v>
+        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
       </c>
       <c r="E18" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F18" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - config reference</v>
       </c>
       <c r="G18" t="str">
-        <v>Rotate immediately if a key ever appears in a commit or a log.</v>
+        <v/>
       </c>
       <c r="H18" t="str">
         <v>No</v>
@@ -1113,10 +1113,10 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D19" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E19" t="str">
         <v>Code walkthrough</v>
@@ -1151,16 +1151,16 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D20" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E20" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F20" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1183,22 +1183,22 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C21" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D21" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E21" t="str">
         <v>Concept</v>
       </c>
       <c r="F21" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1224,19 +1224,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B22" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C22" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D22" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E22" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F22" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1265,16 +1265,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D23" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E23" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F23" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1303,16 +1303,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D24" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E24" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F24" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D25" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E25" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F25" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1379,16 +1379,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D26" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E26" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F26" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1417,16 +1417,16 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D27" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E27" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1455,19 +1455,19 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D28" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E28" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F28" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H28" t="str">
         <v>No</v>
@@ -1487,25 +1487,25 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C29" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D29" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E29" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F29" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G29" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H29" t="str">
         <v>No</v>
@@ -1528,19 +1528,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B30" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C30" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D30" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E30" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1569,16 +1569,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D31" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E31" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1607,16 +1607,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D32" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E32" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1645,16 +1645,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D33" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E33" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D34" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E34" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1715,22 +1715,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C35" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D35" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E35" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1756,19 +1756,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B36" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D36" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E36" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1797,16 +1797,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D37" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E37" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1835,16 +1835,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D38" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E38" t="str">
         <v>Concept</v>
       </c>
       <c r="F38" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,16 +1873,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D39" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E39" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1911,10 +1911,10 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D40" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E40" t="str">
         <v>Hands-on</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D41" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E41" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B42" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C42" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D42" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E42" t="str">
         <v>Concept</v>
       </c>
       <c r="F42" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2022,19 +2022,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B43" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D43" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E43" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2063,19 +2063,19 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D44" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E44" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H44" t="str">
         <v>No</v>
@@ -2101,19 +2101,19 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D45" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E45" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G45" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H45" t="str">
         <v>No</v>
@@ -2139,16 +2139,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D46" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E46" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2177,16 +2177,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D47" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E47" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2209,22 +2209,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C48" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D48" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E48" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2250,19 +2250,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B49" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C49" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D49" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E49" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2291,16 +2291,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D50" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E50" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,16 +2329,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D51" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E51" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D52" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E52" t="str">
         <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D53" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E53" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,19 +2443,19 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D54" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E54" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G54" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H54" t="str">
         <v>No</v>
@@ -2475,25 +2475,25 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C55" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D55" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E55" t="str">
         <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G55" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H55" t="str">
         <v>No</v>
@@ -2516,19 +2516,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B56" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C56" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D56" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E56" t="str">
         <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2557,16 +2557,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D57" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E57" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D58" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E58" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D59" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E59" t="str">
         <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D60" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E60" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D61" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E61" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2741,22 +2741,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C62" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D62" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E62" t="str">
         <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2782,19 +2782,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B63" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D63" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E63" t="str">
         <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,16 +2823,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D64" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E64" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D65" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E65" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D66" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E66" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D67" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E67" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D68" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E68" t="str">
         <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3007,22 +3007,22 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C69" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D69" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E69" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F69" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3048,19 +3048,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B70" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C70" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D70" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E70" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F70" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,16 +3089,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D71" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E71" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,16 +3127,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D72" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E72" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F72" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,16 +3165,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D73" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E73" t="str">
         <v>Concept</v>
       </c>
       <c r="F73" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3203,16 +3203,16 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D74" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E74" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F74" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3241,19 +3241,19 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D75" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E75" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F75" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G75" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H75" t="str">
         <v>No</v>
@@ -3268,50 +3268,12 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B76" t="str">
-        <v/>
-      </c>
-      <c r="C76" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D76" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E76" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F76" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G76" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H76" t="str">
-        <v>No</v>
-      </c>
-      <c r="I76" t="str">
-        <v/>
-      </c>
-      <c r="J76" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K76" t="str">
-        <v/>
-      </c>
-      <c r="L76" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L75"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -1078,7 +1078,7 @@
         <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D18" t="str">
-        <v>Organization, source, region and endpoint settings, batch sizes, timeouts and retry values.</v>
+        <v>Organization, source, region and endpoint settings.</v>
       </c>
       <c r="E18" t="str">
         <v>Code walkthrough</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L74"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -996,16 +996,16 @@
         <v>3. Dashboard configuration to the indexing JAR</v>
       </c>
       <c r="B16" t="str">
-        <v>Trace every piece of console configuration and every key that the indexing JAR depends on.</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>Which Store configuration the JAR depends on</v>
+        <v>API keys the JAR uses and their privileges</v>
       </c>
       <c r="D16" t="str">
-        <v>The source it pushes to, the fields and mappings it assumes exist, and what breaks if any of them changes.</v>
+        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
       </c>
       <c r="E16" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -1037,16 +1037,16 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>API keys the JAR uses and their privileges</v>
+        <v>The JAR configuration file, field by field</v>
       </c>
       <c r="D17" t="str">
-        <v>Minimum privileges for pushing content, one key per environment, and why an admin key is never used.</v>
+        <v>Organization, source, region and endpoint settings.</v>
       </c>
       <c r="E17" t="str">
-        <v>Hands-on</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F17" t="str">
-        <v/>
+        <v>Internal - config reference</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1075,10 +1075,10 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>The JAR configuration file, field by field</v>
+        <v>Configuration per environment and per store</v>
       </c>
       <c r="D18" t="str">
-        <v>Organization, source, region and endpoint settings.</v>
+        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E18" t="str">
         <v>Code walkthrough</v>
@@ -1113,16 +1113,16 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>Configuration per environment and per store</v>
+        <v>Mapping in the console versus mapping in the payload</v>
       </c>
       <c r="D19" t="str">
-        <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
+        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
       </c>
       <c r="E19" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v>Internal - config reference</v>
+        <v>docs.coveo.com - search: mapping rules</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C20" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D20" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E20" t="str">
         <v>Concept</v>
       </c>
       <c r="F20" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1186,19 +1186,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B21" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C21" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D21" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E21" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F21" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1227,16 +1227,16 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D22" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E22" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F22" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1265,16 +1265,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D23" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E23" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F23" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1303,16 +1303,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D24" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E24" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F24" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D25" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E25" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F25" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1379,16 +1379,16 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D26" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E26" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1417,19 +1417,19 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D27" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E27" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H27" t="str">
         <v>No</v>
@@ -1449,25 +1449,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C28" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D28" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E28" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F28" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G28" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H28" t="str">
         <v>No</v>
@@ -1490,19 +1490,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B29" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C29" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D29" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E29" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1531,16 +1531,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D30" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E30" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1569,16 +1569,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D31" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E31" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1607,16 +1607,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D32" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E32" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1645,16 +1645,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D33" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E33" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1677,22 +1677,22 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C34" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D34" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E34" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1718,19 +1718,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B35" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D35" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E35" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1759,16 +1759,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D36" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E36" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1797,16 +1797,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D37" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E37" t="str">
         <v>Concept</v>
       </c>
       <c r="F37" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1835,16 +1835,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D38" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E38" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,10 +1873,10 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D39" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E39" t="str">
         <v>Hands-on</v>
@@ -1911,16 +1911,16 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D40" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E40" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F40" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1943,22 +1943,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C41" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D41" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E41" t="str">
         <v>Concept</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1984,19 +1984,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B42" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C42" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D42" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E42" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2025,19 +2025,19 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D43" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E43" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G43" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H43" t="str">
         <v>No</v>
@@ -2063,19 +2063,19 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D44" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E44" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G44" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H44" t="str">
         <v>No</v>
@@ -2101,16 +2101,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D45" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E45" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2139,16 +2139,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D46" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E46" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2171,22 +2171,22 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B47" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C47" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D47" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E47" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2212,19 +2212,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B48" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C48" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D48" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E48" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,16 +2253,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D49" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E49" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2291,16 +2291,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D50" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E50" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,16 +2329,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D51" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E51" t="str">
         <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D52" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E52" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,19 +2405,19 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D53" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E53" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G53" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H53" t="str">
         <v>No</v>
@@ -2437,25 +2437,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C54" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D54" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E54" t="str">
         <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G54" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H54" t="str">
         <v>No</v>
@@ -2478,19 +2478,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B55" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C55" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D55" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E55" t="str">
         <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,16 +2519,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D56" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E56" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2557,16 +2557,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D57" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E57" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D58" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D59" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E59" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D60" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E60" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2703,22 +2703,22 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C61" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D61" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E61" t="str">
         <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2744,19 +2744,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B62" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D62" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E62" t="str">
         <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D63" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E63" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,16 +2823,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D64" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E64" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D65" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E65" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D66" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E66" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D67" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E67" t="str">
         <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2969,22 +2969,22 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C68" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D68" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E68" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F68" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3010,19 +3010,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B69" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D69" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E69" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F69" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D70" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E70" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,16 +3089,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D71" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E71" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F71" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,16 +3127,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D72" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E72" t="str">
         <v>Concept</v>
       </c>
       <c r="F72" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,16 +3165,16 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D73" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E73" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F73" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3203,19 +3203,19 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D74" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E74" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F74" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G74" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H74" t="str">
         <v>No</v>
@@ -3230,50 +3230,12 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B75" t="str">
-        <v/>
-      </c>
-      <c r="C75" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D75" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E75" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F75" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G75" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H75" t="str">
-        <v>No</v>
-      </c>
-      <c r="I75" t="str">
-        <v/>
-      </c>
-      <c r="J75" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K75" t="str">
-        <v/>
-      </c>
-      <c r="L75" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L74"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -1043,7 +1043,7 @@
         <v>Organization, source, region and endpoint settings.</v>
       </c>
       <c r="E17" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F17" t="str">
         <v>Internal - config reference</v>
@@ -1081,7 +1081,7 @@
         <v>How one JAR serves several organizations and stores, and how the right configuration is selected at run time.</v>
       </c>
       <c r="E18" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F18" t="str">
         <v>Internal - config reference</v>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -1122,7 +1122,7 @@
         <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v>docs.coveo.com - search: mapping rules</v>
+        <v/>
       </c>
       <c r="G19" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L73"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1107,22 +1107,22 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
       </c>
       <c r="C19" t="str">
-        <v>Mapping in the console versus mapping in the payload</v>
+        <v>End-to-end shape of an indexing run</v>
       </c>
       <c r="D19" t="str">
-        <v>Which values are set by the push payload, which by source mappings, and which wins.</v>
+        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
       </c>
       <c r="E19" t="str">
         <v>Concept</v>
       </c>
       <c r="F19" t="str">
-        <v/>
+        <v>Internal - architecture diagram</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1148,19 +1148,19 @@
         <v>4. Indexing JAR, process and code walkthrough</v>
       </c>
       <c r="B20" t="str">
-        <v>Read the JAR, run it against non-prod, and explain each stage of a run.</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>End-to-end shape of an indexing run</v>
+        <v>Project layout and entry points</v>
       </c>
       <c r="D20" t="str">
-        <v>Trigger, fetch from the source system, transform, push to Coveo, report. Where each step can stop.</v>
+        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
       </c>
       <c r="E20" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F20" t="str">
-        <v>Internal - architecture diagram</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1189,16 +1189,16 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>Project layout and entry points</v>
+        <v>Data model and item identifiers</v>
       </c>
       <c r="D21" t="str">
-        <v>Modules, main class, how the JAR is built and versioned, and where to start reading.</v>
+        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
       </c>
       <c r="E21" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F21" t="str">
-        <v>Internal - repository</v>
+        <v>docs.coveo.com - search: item identifier</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1227,16 +1227,16 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>Data model and item identifiers</v>
+        <v>Batch push and Stream API</v>
       </c>
       <c r="D22" t="str">
-        <v>The fields we send, how an item URI or permanent ID is composed, and why a stable identifier matters.</v>
+        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
       </c>
       <c r="E22" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F22" t="str">
-        <v>docs.coveo.com - search: item identifier</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1265,16 +1265,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Batch push and Stream API</v>
+        <v>Full rebuild, delta run and deletions</v>
       </c>
       <c r="D23" t="str">
-        <v>Single item, batch and stream operations. Which the JAR uses for a delta run and which for a rebuild.</v>
+        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
       </c>
       <c r="E23" t="str">
-        <v>Code walkthrough</v>
+        <v>Concept</v>
       </c>
       <c r="F23" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: delete items</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1303,16 +1303,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Scheduling, retries and idempotency</v>
       </c>
       <c r="D24" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
       </c>
       <c r="E24" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F24" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v>Internal - repository</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,16 +1341,16 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D25" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E25" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1379,19 +1379,19 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D26" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E26" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H26" t="str">
         <v>No</v>
@@ -1411,25 +1411,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B27" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C27" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D27" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E27" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F27" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G27" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H27" t="str">
         <v>No</v>
@@ -1452,19 +1452,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B28" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C28" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D28" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E28" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1493,16 +1493,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D29" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E29" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1531,16 +1531,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D30" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E30" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1569,16 +1569,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D31" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E31" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1607,16 +1607,16 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D32" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E32" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C33" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D33" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E33" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1680,19 +1680,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B34" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C34" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D34" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E34" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D35" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E35" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1759,16 +1759,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D36" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E36" t="str">
         <v>Concept</v>
       </c>
       <c r="F36" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1797,16 +1797,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D37" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E37" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1835,10 +1835,10 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D38" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E38" t="str">
         <v>Hands-on</v>
@@ -1873,16 +1873,16 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D39" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E39" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F39" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1905,22 +1905,22 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C40" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D40" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E40" t="str">
         <v>Concept</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1946,19 +1946,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B41" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D41" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E41" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1987,19 +1987,19 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D42" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E42" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H42" t="str">
         <v>No</v>
@@ -2025,19 +2025,19 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D43" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E43" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G43" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H43" t="str">
         <v>No</v>
@@ -2063,16 +2063,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D44" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E44" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2101,16 +2101,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D45" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E45" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C46" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D46" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E46" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2174,19 +2174,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B47" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C47" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D47" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E47" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D48" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E48" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,16 +2253,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D49" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E49" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2291,16 +2291,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D50" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E50" t="str">
         <v>Concept</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,16 +2329,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D51" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E51" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,19 +2367,19 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D52" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E52" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G52" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H52" t="str">
         <v>No</v>
@@ -2399,25 +2399,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C53" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D53" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E53" t="str">
         <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G53" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H53" t="str">
         <v>No</v>
@@ -2440,19 +2440,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B54" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C54" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D54" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E54" t="str">
         <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,16 +2481,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D55" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E55" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,16 +2519,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D56" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E56" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2557,16 +2557,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D57" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E57" t="str">
         <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D58" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E58" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D59" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E59" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2665,22 +2665,22 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C60" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D60" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2706,19 +2706,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B61" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D61" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E61" t="str">
         <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D62" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E62" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D63" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E63" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,16 +2823,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D64" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E64" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D65" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E65" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D66" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E66" t="str">
         <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C67" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D67" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E67" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F67" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2972,19 +2972,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B68" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D68" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E68" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F68" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D69" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E69" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D70" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E70" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F70" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,16 +3089,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D71" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E71" t="str">
         <v>Concept</v>
       </c>
       <c r="F71" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,16 +3127,16 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D72" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E72" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F72" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3165,19 +3165,19 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D73" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E73" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F73" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G73" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H73" t="str">
         <v>No</v>
@@ -3192,50 +3192,12 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B74" t="str">
-        <v/>
-      </c>
-      <c r="C74" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D74" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E74" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F74" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G74" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H74" t="str">
-        <v>No</v>
-      </c>
-      <c r="I74" t="str">
-        <v/>
-      </c>
-      <c r="J74" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
-      <c r="L74" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L73"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -993,7 +993,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>3. Dashboard configuration to the run indexing JAR</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>3. Dashboard configuration to the run indexing JAR</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>3. Dashboard configuration to the indexing JAR</v>
+        <v>3. Dashboard configuration to the run indexing JAR</v>
       </c>
       <c r="B18" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L72"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1303,16 +1303,16 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>Scheduling, retries and idempotency</v>
+        <v>Logging, metrics and run records</v>
       </c>
       <c r="D24" t="str">
-        <v>How runs are scheduled, what happens on overlap, and why a rerun must be safe.</v>
+        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
       </c>
       <c r="E24" t="str">
         <v>Code walkthrough</v>
       </c>
       <c r="F24" t="str">
-        <v>Internal - repository</v>
+        <v>Internal - logging</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1341,19 +1341,19 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>Logging, metrics and run records</v>
+        <v>Run the JAR yourself against non-prod</v>
       </c>
       <c r="D25" t="str">
-        <v>What the JAR logs, where the logs go, and what a healthy run looks like.</v>
+        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
       </c>
       <c r="E25" t="str">
-        <v>Code walkthrough</v>
+        <v>Hands-on</v>
       </c>
       <c r="F25" t="str">
-        <v>Internal - logging</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>The first real exit check for this stage.</v>
       </c>
       <c r="H25" t="str">
         <v>No</v>
@@ -1373,25 +1373,25 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>4. Indexing JAR, process and code walkthrough</v>
+        <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
       </c>
       <c r="C26" t="str">
-        <v>Run the JAR yourself against non-prod</v>
+        <v>Push API: add, update and delete</v>
       </c>
       <c r="D26" t="str">
-        <v>Build, configure and execute a run, then confirm the result in the Content Browser.</v>
+        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
       </c>
       <c r="E26" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F26" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Push API</v>
       </c>
       <c r="G26" t="str">
-        <v>The first real exit check for this stage.</v>
+        <v/>
       </c>
       <c r="H26" t="str">
         <v>No</v>
@@ -1414,19 +1414,19 @@
         <v>5. Coveo APIs used by the JAR, and Swagger</v>
       </c>
       <c r="B27" t="str">
-        <v>Call the Coveo APIs the JAR uses directly, and read the API reference unaided.</v>
+        <v/>
       </c>
       <c r="C27" t="str">
-        <v>Push API: add, update and delete</v>
+        <v>Stream API: open, chunk, close</v>
       </c>
       <c r="D27" t="str">
-        <v>The endpoints the JAR calls, required headers, payload shape and expected responses.</v>
+        <v>When a stream is the right choice and what happens if a stream is left open.</v>
       </c>
       <c r="E27" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F27" t="str">
-        <v>docs.coveo.com - search: Push API</v>
+        <v>docs.coveo.com - search: Stream API</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1455,16 +1455,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Stream API: open, chunk, close</v>
+        <v>Source status and activity endpoints</v>
       </c>
       <c r="D28" t="str">
-        <v>When a stream is the right choice and what happens if a stream is left open.</v>
+        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
       </c>
       <c r="E28" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: Stream API</v>
+        <v>docs.coveo.com - search: source status</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1493,16 +1493,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D29" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E29" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1531,16 +1531,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D30" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E30" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1569,16 +1569,16 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D31" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E31" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1601,22 +1601,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C32" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D32" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E32" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1642,19 +1642,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B33" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D33" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E33" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D34" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E34" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D35" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E35" t="str">
         <v>Concept</v>
       </c>
       <c r="F35" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1759,16 +1759,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D36" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E36" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1797,10 +1797,10 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D37" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E37" t="str">
         <v>Hands-on</v>
@@ -1835,16 +1835,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D38" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E38" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F38" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1867,22 +1867,22 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C39" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D39" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E39" t="str">
         <v>Concept</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1908,19 +1908,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B40" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D40" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E40" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F40" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1949,19 +1949,19 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D41" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E41" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G41" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H41" t="str">
         <v>No</v>
@@ -1987,19 +1987,19 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D42" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E42" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G42" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H42" t="str">
         <v>No</v>
@@ -2025,16 +2025,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D43" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E43" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2063,16 +2063,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D44" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E44" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2095,22 +2095,22 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C45" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D45" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E45" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2136,19 +2136,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B46" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C46" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D46" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E46" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2177,16 +2177,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D47" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E47" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D48" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E48" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,16 +2253,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D49" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E49" t="str">
         <v>Concept</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2291,16 +2291,16 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D50" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E50" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,19 +2329,19 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D51" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E51" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G51" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H51" t="str">
         <v>No</v>
@@ -2361,25 +2361,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C52" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D52" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E52" t="str">
         <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G52" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H52" t="str">
         <v>No</v>
@@ -2402,19 +2402,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B53" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D53" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E53" t="str">
         <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D54" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E54" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,16 +2481,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D55" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E55" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,16 +2519,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D56" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E56" t="str">
         <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2557,16 +2557,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D57" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E57" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D58" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E58" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C59" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D59" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E59" t="str">
         <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2668,19 +2668,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B60" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D60" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D61" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E61" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D62" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E62" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D63" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E63" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,16 +2823,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D64" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E64" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D65" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E65" t="str">
         <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2893,22 +2893,22 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C66" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D66" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E66" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F66" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2934,19 +2934,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B67" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D67" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E67" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F67" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D68" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E68" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D69" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E69" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D70" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E70" t="str">
         <v>Concept</v>
       </c>
       <c r="F70" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,16 +3089,16 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D71" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E71" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F71" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3127,19 +3127,19 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D72" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E72" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F72" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G72" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H72" t="str">
         <v>No</v>
@@ -3154,50 +3154,12 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B73" t="str">
-        <v/>
-      </c>
-      <c r="C73" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D73" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E73" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F73" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G73" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H73" t="str">
-        <v>No</v>
-      </c>
-      <c r="I73" t="str">
-        <v/>
-      </c>
-      <c r="J73" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K73" t="str">
-        <v/>
-      </c>
-      <c r="L73" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L72"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -1265,16 +1265,16 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>Full rebuild, delta run and deletions</v>
+        <v>Non-Catalog  data indexing using Push API's</v>
       </c>
       <c r="D23" t="str">
-        <v>How a full run differs from an incremental one, and how removals reach the index.</v>
+        <v>Indexing Datasheets, Content page, location, Faq's, MyAccount</v>
       </c>
       <c r="E23" t="str">
-        <v>Concept</v>
+        <v>Code walkthrough</v>
       </c>
       <c r="F23" t="str">
-        <v>docs.coveo.com - search: delete items</v>
+        <v/>
       </c>
       <c r="G23" t="str">
         <v/>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L71"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1455,16 +1455,16 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>Source status and activity endpoints</v>
+        <v>Fields and mappings management APIs</v>
       </c>
       <c r="D28" t="str">
-        <v>Setting source status, reading activity, and using it to confirm a run landed.</v>
+        <v>Creating and editing fields and mappings through the API rather than the console.</v>
       </c>
       <c r="E28" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F28" t="str">
-        <v>docs.coveo.com - search: source status</v>
+        <v>docs.coveo.com - search: fields API</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1493,16 +1493,16 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>Fields and mappings management APIs</v>
+        <v>Swagger and the API reference walkthrough</v>
       </c>
       <c r="D29" t="str">
-        <v>Creating and editing fields and mappings through the API rather than the console.</v>
+        <v>Authenticating in the reference, running a call, reading request and response models.</v>
       </c>
       <c r="E29" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F29" t="str">
-        <v>docs.coveo.com - search: fields API</v>
+        <v>docs.coveo.com - search: API reference</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1531,16 +1531,16 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>Swagger and the API reference walkthrough</v>
+        <v>Limits and error codes</v>
       </c>
       <c r="D30" t="str">
-        <v>Authenticating in the reference, running a call, reading request and response models.</v>
+        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
       </c>
       <c r="E30" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F30" t="str">
-        <v>docs.coveo.com - search: API reference</v>
+        <v>docs.coveo.com - search: API error codes</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1563,22 +1563,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>5. Coveo APIs used by the JAR, and Swagger</v>
+        <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Take a failed indexing run and get to the cause without escalating.</v>
       </c>
       <c r="C31" t="str">
-        <v>Limits and error codes</v>
+        <v>Read a failed run: JAR log and Coveo activity</v>
       </c>
       <c r="D31" t="str">
-        <v>Rate limits, payload size limits, and what each HTTP status from Coveo actually means for a run.</v>
+        <v>Line up the JAR's own error with the source activity entry in the console.</v>
       </c>
       <c r="E31" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F31" t="str">
-        <v>docs.coveo.com - search: API error codes</v>
+        <v>docs.coveo.com - search: source activity</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1604,19 +1604,19 @@
         <v>6. Indexing failure debug and config validation</v>
       </c>
       <c r="B32" t="str">
-        <v>Take a failed indexing run and get to the cause without escalating.</v>
+        <v/>
       </c>
       <c r="C32" t="str">
-        <v>Read a failed run: JAR log and Coveo activity</v>
+        <v>Confirm an item in the Content Browser</v>
       </c>
       <c r="D32" t="str">
-        <v>Line up the JAR's own error with the source activity entry in the console.</v>
+        <v>Check that an item exists, and inspect its fields and permissions.</v>
       </c>
       <c r="E32" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F32" t="str">
-        <v>docs.coveo.com - search: source activity</v>
+        <v>docs.coveo.com - search: Content Browser</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1645,16 +1645,16 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>Confirm an item in the Content Browser</v>
+        <v>The failures we actually see</v>
       </c>
       <c r="D33" t="str">
-        <v>Check that an item exists, and inspect its fields and permissions.</v>
+        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
       </c>
       <c r="E33" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F33" t="str">
-        <v>docs.coveo.com - search: Content Browser</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>The failures we actually see</v>
+        <v>Item-level error versus rejected batch</v>
       </c>
       <c r="D34" t="str">
-        <v>Bad or missing mapping, missing field, expired or under-privileged key, payload too large, malformed JSON, source in the wrong state.</v>
+        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
       </c>
       <c r="E34" t="str">
         <v>Concept</v>
       </c>
       <c r="F34" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: push error</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,16 +1721,16 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D35" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E35" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F35" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1759,10 +1759,10 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D36" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E36" t="str">
         <v>Hands-on</v>
@@ -1797,16 +1797,16 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D37" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E37" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F37" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1829,22 +1829,22 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C38" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D38" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E38" t="str">
         <v>Concept</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1870,19 +1870,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B39" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D39" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E39" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F39" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1911,19 +1911,19 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D40" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E40" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F40" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G40" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H40" t="str">
         <v>No</v>
@@ -1949,19 +1949,19 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D41" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E41" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G41" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H41" t="str">
         <v>No</v>
@@ -1987,16 +1987,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D42" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E42" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2025,16 +2025,16 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D43" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E43" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2057,22 +2057,22 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C44" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D44" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E44" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2098,19 +2098,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B45" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C45" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D45" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E45" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2139,16 +2139,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D46" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E46" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2177,16 +2177,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D47" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E47" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D48" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E48" t="str">
         <v>Concept</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,16 +2253,16 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D49" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E49" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2291,19 +2291,19 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D50" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E50" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G50" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H50" t="str">
         <v>No</v>
@@ -2323,25 +2323,25 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C51" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D51" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E51" t="str">
         <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G51" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H51" t="str">
         <v>No</v>
@@ -2364,19 +2364,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B52" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C52" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D52" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E52" t="str">
         <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D53" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E53" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D54" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E54" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,16 +2481,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D55" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E55" t="str">
         <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,16 +2519,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D56" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E56" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F56" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2557,16 +2557,16 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D57" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E57" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2589,22 +2589,22 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C58" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D58" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2630,19 +2630,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B59" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D59" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E59" t="str">
         <v>Concept</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D60" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E60" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D61" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E61" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D62" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E62" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D63" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E63" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2823,16 +2823,16 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D64" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E64" t="str">
         <v>Concept</v>
       </c>
       <c r="F64" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C65" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D65" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E65" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F65" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2896,19 +2896,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B66" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D66" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E66" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F66" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D67" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E67" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D68" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E68" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D69" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E69" t="str">
         <v>Concept</v>
       </c>
       <c r="F69" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,16 +3051,16 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D70" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E70" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F70" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3089,19 +3089,19 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D71" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E71" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F71" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G71" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H71" t="str">
         <v>No</v>
@@ -3116,50 +3116,12 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B72" t="str">
-        <v/>
-      </c>
-      <c r="C72" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D72" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E72" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F72" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G72" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H72" t="str">
-        <v>No</v>
-      </c>
-      <c r="I72" t="str">
-        <v/>
-      </c>
-      <c r="J72" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K72" t="str">
-        <v/>
-      </c>
-      <c r="L72" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L70"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1683,16 +1683,16 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>Item-level error versus rejected batch</v>
+        <v>Configuration validation checklist</v>
       </c>
       <c r="D34" t="str">
-        <v>Telling a single bad item apart from a whole batch that never landed, and what each needs.</v>
+        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
       </c>
       <c r="E34" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F34" t="str">
-        <v>docs.coveo.com - search: push error</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1721,10 +1721,10 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>Configuration validation checklist</v>
+        <v>Re-drive a failed batch safely</v>
       </c>
       <c r="D35" t="str">
-        <v>What to re-check after any configuration change, in order, before declaring a run healthy.</v>
+        <v>Replaying without duplicating items or wiping good content.</v>
       </c>
       <c r="E35" t="str">
         <v>Hands-on</v>
@@ -1759,16 +1759,16 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Rebuild, refresh and rescan</v>
       </c>
       <c r="D36" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>What each does, what it costs, and how to choose under time pressure.</v>
       </c>
       <c r="E36" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F36" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: refresh rescan rebuild</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1791,22 +1791,22 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C37" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D37" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E37" t="str">
         <v>Concept</v>
       </c>
       <c r="F37" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1832,19 +1832,19 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B38" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D38" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E38" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F38" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,19 +1873,19 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D39" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E39" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F39" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H39" t="str">
         <v>No</v>
@@ -1911,19 +1911,19 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D40" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E40" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F40" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G40" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H40" t="str">
         <v>No</v>
@@ -1949,16 +1949,16 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>Non-prod parity check</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D41" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E41" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1987,16 +1987,16 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D42" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E42" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - go-live plan</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2019,22 +2019,22 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C43" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Read a search response</v>
       </c>
       <c r="D43" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E43" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F43" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2060,19 +2060,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B44" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C44" t="str">
-        <v>Read a search response</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D44" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E44" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F44" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2101,16 +2101,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D45" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E45" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2139,16 +2139,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Relevance inspector</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D46" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E46" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2177,16 +2177,16 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>Analytics event types</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D47" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E47" t="str">
         <v>Concept</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2215,16 +2215,16 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>How events reach Coveo</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D48" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E48" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2253,19 +2253,19 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Follow one visit end to end</v>
+        <v>Event data quality</v>
       </c>
       <c r="D49" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E49" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G49" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H49" t="str">
         <v>No</v>
@@ -2285,25 +2285,25 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B50" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C50" t="str">
-        <v>Event data quality</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D50" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E50" t="str">
         <v>Concept</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G50" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H50" t="str">
         <v>No</v>
@@ -2326,19 +2326,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B51" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C51" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D51" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E51" t="str">
         <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D52" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E52" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D53" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E53" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D54" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E54" t="str">
         <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2481,16 +2481,16 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D55" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E55" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F55" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2519,16 +2519,16 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D56" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E56" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C57" t="str">
-        <v>Change control for merchandising</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D57" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E57" t="str">
         <v>Concept</v>
       </c>
       <c r="F57" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2592,19 +2592,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B58" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>The model catalogue</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D58" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D59" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E59" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D60" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E60" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Commerce model specifics</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D61" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E61" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2747,16 +2747,16 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D62" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E62" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2785,16 +2785,16 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D63" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E63" t="str">
         <v>Concept</v>
       </c>
       <c r="F63" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2817,22 +2817,22 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C64" t="str">
-        <v>What silently breaks a model</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D64" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E64" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F64" t="str">
-        <v>Internal - incident history</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2858,19 +2858,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B65" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>Routine health checks</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D65" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E65" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F65" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D66" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E66" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D67" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E67" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F67" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,16 +2975,16 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D68" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E68" t="str">
         <v>Concept</v>
       </c>
       <c r="F68" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -3013,16 +3013,16 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>Support and escalation</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D69" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E69" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F69" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3051,19 +3051,19 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>Documentation and ownership handover</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D70" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E70" t="str">
-        <v>Reading</v>
+        <v>Shadowing</v>
       </c>
       <c r="F70" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal</v>
       </c>
       <c r="G70" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H70" t="str">
         <v>No</v>
@@ -3078,50 +3078,12 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B71" t="str">
-        <v/>
-      </c>
-      <c r="C71" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D71" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E71" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F71" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G71" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H71" t="str">
-        <v>No</v>
-      </c>
-      <c r="I71" t="str">
-        <v/>
-      </c>
-      <c r="J71" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K71" t="str">
-        <v/>
-      </c>
-      <c r="L71" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L71"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L70"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L68"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -1715,22 +1715,22 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
       </c>
       <c r="C35" t="str">
-        <v>Re-drive a failed batch safely</v>
+        <v>Go-live checklist for a new store</v>
       </c>
       <c r="D35" t="str">
-        <v>Replaying without duplicating items or wiping good content.</v>
+        <v>Every configuration item and key needed before a store can serve traffic.</v>
       </c>
       <c r="E35" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F35" t="str">
-        <v>Internal - runbook</v>
+        <v>Internal - go-live checklist</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6. Indexing failure debug and config validation</v>
+        <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>Rebuild, refresh and rescan</v>
+        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
       </c>
       <c r="D36" t="str">
-        <v>What each does, what it costs, and how to choose under time pressure.</v>
+        <v>What is created per store, what is shared, and the naming we follow.</v>
       </c>
       <c r="E36" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F36" t="str">
-        <v>docs.coveo.com - search: refresh rescan rebuild</v>
+        <v>docs.coveo.com - search: search hub</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1794,22 +1794,22 @@
         <v>7. Store go-live validation and keys</v>
       </c>
       <c r="B37" t="str">
-        <v>Validate and cut over a new store on your own, with a rollback ready.</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v>Go-live checklist for a new store</v>
+        <v>Keys and access for the new environment</v>
       </c>
       <c r="D37" t="str">
-        <v>Every configuration item and key needed before a store can serve traffic.</v>
+        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
       </c>
       <c r="E37" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F37" t="str">
-        <v>Internal - go-live checklist</v>
+        <v>Internal - secret management</v>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>Values go in the secret store only.</v>
       </c>
       <c r="H37" t="str">
         <v>No</v>
@@ -1835,16 +1835,16 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>Store configuration: catalog, source, pipeline, search hub, fields</v>
+        <v>Non-prod parity check</v>
       </c>
       <c r="D38" t="str">
-        <v>What is created per store, what is shared, and the naming we follow.</v>
+        <v>Proving non-prod and prod configuration match before cutover.</v>
       </c>
       <c r="E38" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F38" t="str">
-        <v>docs.coveo.com - search: search hub</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1873,19 +1873,19 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>Keys and access for the new environment</v>
+        <v>Cutover sequence and rollback</v>
       </c>
       <c r="D39" t="str">
-        <v>Requesting keys, confirming privileges, and recording them in the secret store.</v>
+        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
       </c>
       <c r="E39" t="str">
-        <v>Hands-on</v>
+        <v>Shadowing</v>
       </c>
       <c r="F39" t="str">
-        <v>Internal - secret management</v>
+        <v>Internal - go-live plan</v>
       </c>
       <c r="G39" t="str">
-        <v>Values go in the secret store only.</v>
+        <v/>
       </c>
       <c r="H39" t="str">
         <v>No</v>
@@ -1911,10 +1911,10 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>Non-prod parity check</v>
+        <v>Post-go-live smoke checks</v>
       </c>
       <c r="D40" t="str">
-        <v>Proving non-prod and prod configuration match before cutover.</v>
+        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
       </c>
       <c r="E40" t="str">
         <v>Hands-on</v>
@@ -1943,22 +1943,22 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Follow one user journey from the search response through to the analytics record.</v>
       </c>
       <c r="C41" t="str">
-        <v>Cutover sequence and rollback</v>
+        <v>Read a search response</v>
       </c>
       <c r="D41" t="str">
-        <v>Order of operations on go-live day, who signs off, and how we roll back.</v>
+        <v>Response structure, returned fields, ranking information, and total counts.</v>
       </c>
       <c r="E41" t="str">
-        <v>Shadowing</v>
+        <v>Hands-on</v>
       </c>
       <c r="F41" t="str">
-        <v>Internal - go-live plan</v>
+        <v>docs.coveo.com - search: Search API response</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>7. Store go-live validation and keys</v>
+        <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>Post-go-live smoke checks</v>
+        <v>Debug mode and the execution report</v>
       </c>
       <c r="D42" t="str">
-        <v>Indexed counts, sample queries, facets, and analytics events arriving.</v>
+        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
       </c>
       <c r="E42" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F42" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: execution report</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2022,19 +2022,19 @@
         <v>8. Response inspector, analytics and user journey</v>
       </c>
       <c r="B43" t="str">
-        <v>Follow one user journey from the search response through to the analytics record.</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v>Read a search response</v>
+        <v>Relevance inspector</v>
       </c>
       <c r="D43" t="str">
-        <v>Response structure, returned fields, ranking information, and total counts.</v>
+        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
       </c>
       <c r="E43" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F43" t="str">
-        <v>docs.coveo.com - search: Search API response</v>
+        <v>docs.coveo.com - search: relevance inspector</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2063,16 +2063,16 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>Debug mode and the execution report</v>
+        <v>Analytics event types</v>
       </c>
       <c r="D44" t="str">
-        <v>Appending debug to a query and reading the execution report to see what the pipeline did.</v>
+        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
       </c>
       <c r="E44" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F44" t="str">
-        <v>docs.coveo.com - search: execution report</v>
+        <v>docs.coveo.com - search: usage analytics events</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2101,16 +2101,16 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>Relevance inspector</v>
+        <v>How events reach Coveo</v>
       </c>
       <c r="D45" t="str">
-        <v>Opening the inspector, reading ranking contributions, and spotting an over-boosted pipeline.</v>
+        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
       </c>
       <c r="E45" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F45" t="str">
-        <v>docs.coveo.com - search: relevance inspector</v>
+        <v>docs.coveo.com - search: send analytics events</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2139,16 +2139,16 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>Analytics event types</v>
+        <v>Follow one visit end to end</v>
       </c>
       <c r="D46" t="str">
-        <v>Search, click, custom, view and commerce events, and which of them we depend on.</v>
+        <v>Take a single visit and trace query, results, clicks and conversion.</v>
       </c>
       <c r="E46" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F46" t="str">
-        <v>docs.coveo.com - search: usage analytics events</v>
+        <v>docs.coveo.com - search: visit browser</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2177,19 +2177,19 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>How events reach Coveo</v>
+        <v>Event data quality</v>
       </c>
       <c r="D47" t="str">
-        <v>What the front end sends, what we send server-side, and the fields that must be present.</v>
+        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
       </c>
       <c r="E47" t="str">
         <v>Concept</v>
       </c>
       <c r="F47" t="str">
-        <v>docs.coveo.com - search: send analytics events</v>
+        <v>docs.coveo.com - search: analytics data health</v>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>Bad events quietly degrade every model.</v>
       </c>
       <c r="H47" t="str">
         <v>No</v>
@@ -2209,22 +2209,22 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
       </c>
       <c r="C48" t="str">
-        <v>Follow one visit end to end</v>
+        <v>What the Merchandising Hub is and who uses it</v>
       </c>
       <c r="D48" t="str">
-        <v>Take a single visit and trace query, results, clicks and conversion.</v>
+        <v>The split between business-owned merchandising and our configuration.</v>
       </c>
       <c r="E48" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F48" t="str">
-        <v>docs.coveo.com - search: visit browser</v>
+        <v>docs.coveo.com - search: Merchandising Hub</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2247,25 +2247,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>8. Response inspector, analytics and user journey</v>
+        <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>Event data quality</v>
+        <v>Product listings and catalog configuration behind it</v>
       </c>
       <c r="D49" t="str">
-        <v>Missing, duplicated or mistyped events, how we detect them, and what they break downstream.</v>
+        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
       </c>
       <c r="E49" t="str">
         <v>Concept</v>
       </c>
       <c r="F49" t="str">
-        <v>docs.coveo.com - search: analytics data health</v>
+        <v>docs.coveo.com - search: product listing configuration</v>
       </c>
       <c r="G49" t="str">
-        <v>Bad events quietly degrade every model.</v>
+        <v/>
       </c>
       <c r="H49" t="str">
         <v>No</v>
@@ -2288,19 +2288,19 @@
         <v>9. Merchandising Hub rules and configuration</v>
       </c>
       <c r="B50" t="str">
-        <v>Support merchandising rules and explain why a rule did or didn't take effect.</v>
+        <v/>
       </c>
       <c r="C50" t="str">
-        <v>What the Merchandising Hub is and who uses it</v>
+        <v>Rule types and what each one does</v>
       </c>
       <c r="D50" t="str">
-        <v>The split between business-owned merchandising and our configuration.</v>
+        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
       </c>
       <c r="E50" t="str">
-        <v>Concept</v>
+        <v>Demo</v>
       </c>
       <c r="F50" t="str">
-        <v>docs.coveo.com - search: Merchandising Hub</v>
+        <v>docs.coveo.com - search: merchandising rules</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2329,16 +2329,16 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>Product listings and catalog configuration behind it</v>
+        <v>Merchandising rules versus query pipeline statements</v>
       </c>
       <c r="D51" t="str">
-        <v>Catalog structure, product grouping and availability, and what the hub relies on from the index.</v>
+        <v>Which layer to use for which requirement, and how they interact.</v>
       </c>
       <c r="E51" t="str">
         <v>Concept</v>
       </c>
       <c r="F51" t="str">
-        <v>docs.coveo.com - search: product listing configuration</v>
+        <v>docs.coveo.com - search: ranking rules</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2367,16 +2367,16 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>Rule types and what each one does</v>
+        <v>Index-side requirements for merchandising</v>
       </c>
       <c r="D52" t="str">
-        <v>Boost, bury, pin, block and filter rules, and their order of effect.</v>
+        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
       </c>
       <c r="E52" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F52" t="str">
-        <v>docs.coveo.com - search: merchandising rules</v>
+        <v>docs.coveo.com - search: catalog fields</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2405,16 +2405,16 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>Merchandising rules versus query pipeline statements</v>
+        <v>Troubleshoot a rule that has no effect</v>
       </c>
       <c r="D53" t="str">
-        <v>Which layer to use for which requirement, and how they interact.</v>
+        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
       </c>
       <c r="E53" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F53" t="str">
-        <v>docs.coveo.com - search: ranking rules</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2443,16 +2443,16 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>Index-side requirements for merchandising</v>
+        <v>Change control for merchandising</v>
       </c>
       <c r="D54" t="str">
-        <v>Fields, availability data and grouping that must be indexed correctly for rules to work.</v>
+        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
       </c>
       <c r="E54" t="str">
         <v>Concept</v>
       </c>
       <c r="F54" t="str">
-        <v>docs.coveo.com - search: catalog fields</v>
+        <v>Internal - ways of working</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
       </c>
       <c r="C55" t="str">
-        <v>Troubleshoot a rule that has no effect</v>
+        <v>The model catalogue</v>
       </c>
       <c r="D55" t="str">
-        <v>Check the listing, the condition, the pipeline, then the underlying data.</v>
+        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
       </c>
       <c r="E55" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F55" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2513,22 +2513,22 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>9. Merchandising Hub rules and configuration</v>
+        <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>Change control for merchandising</v>
+        <v>What each model needs before it can work</v>
       </c>
       <c r="D56" t="str">
-        <v>Who approves, where changes are recorded, and how a rule is reverted.</v>
+        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
       </c>
       <c r="E56" t="str">
         <v>Concept</v>
       </c>
       <c r="F56" t="str">
-        <v>Internal - ways of working</v>
+        <v>docs.coveo.com - search: model requirements</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2554,19 +2554,19 @@
         <v>10. Coveo models walkthrough and configuration</v>
       </c>
       <c r="B57" t="str">
-        <v>Know which model solves which problem, what data it needs, and how it is wired to a pipeline.</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>The model catalogue</v>
+        <v>Create a model and associate it with a pipeline</v>
       </c>
       <c r="D57" t="str">
-        <v>ART, Query Suggestions and Predictive QS, DNE, Content Recommendations, Product Recommendations and IAPR, Smart Snippets, Relevance Generative Answering with its Semantic Encoder, Case Classification.</v>
+        <v>Configuration options, conditions, association order, and what order means at query time.</v>
       </c>
       <c r="E57" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F57" t="str">
-        <v>docs.coveo.com - search: Coveo Machine Learning models</v>
+        <v>docs.coveo.com - search: model associations</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2595,16 +2595,16 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>What each model needs before it can work</v>
+        <v>Commerce model specifics</v>
       </c>
       <c r="D58" t="str">
-        <v>Event volume, content scope and field requirements. Why a model can sit idle.</v>
+        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
       </c>
       <c r="E58" t="str">
         <v>Concept</v>
       </c>
       <c r="F58" t="str">
-        <v>docs.coveo.com - search: model requirements</v>
+        <v>docs.coveo.com - search: Product Recommendations</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2633,16 +2633,16 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>Create a model and associate it with a pipeline</v>
+        <v>Training schedule, status and candidate review</v>
       </c>
       <c r="D59" t="str">
-        <v>Configuration options, conditions, association order, and what order means at query time.</v>
+        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
       </c>
       <c r="E59" t="str">
-        <v>Hands-on</v>
+        <v>Demo</v>
       </c>
       <c r="F59" t="str">
-        <v>docs.coveo.com - search: model associations</v>
+        <v>docs.coveo.com - search: review model information</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2671,16 +2671,16 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>Commerce model specifics</v>
+        <v>A/B testing a pipeline change</v>
       </c>
       <c r="D60" t="str">
-        <v>Product recommendations and intent-aware ranking, and the catalog data they depend on.</v>
+        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
       </c>
       <c r="E60" t="str">
         <v>Concept</v>
       </c>
       <c r="F60" t="str">
-        <v>docs.coveo.com - search: Product Recommendations</v>
+        <v>docs.coveo.com - search: A/B test</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2709,16 +2709,16 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>Training schedule, status and candidate review</v>
+        <v>What silently breaks a model</v>
       </c>
       <c r="D61" t="str">
-        <v>When models retrain, how to read status, and how to review what a model would suggest.</v>
+        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
       </c>
       <c r="E61" t="str">
-        <v>Demo</v>
+        <v>Concept</v>
       </c>
       <c r="F61" t="str">
-        <v>docs.coveo.com - search: review model information</v>
+        <v>Internal - incident history</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2741,22 +2741,22 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Run and audit the configuration day to day, and know when to escalate.</v>
       </c>
       <c r="C62" t="str">
-        <v>A/B testing a pipeline change</v>
+        <v>Routine health checks</v>
       </c>
       <c r="D62" t="str">
-        <v>Setting up a split, choosing the metric, and how long to leave it running.</v>
+        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
       </c>
       <c r="E62" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F62" t="str">
-        <v>docs.coveo.com - search: A/B test</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10. Coveo models walkthrough and configuration</v>
+        <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>What silently breaks a model</v>
+        <v>Resource snapshots and promoting configuration</v>
       </c>
       <c r="D63" t="str">
-        <v>Event gaps, renamed fields, changed permissions, reindexing without care.</v>
+        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
       </c>
       <c r="E63" t="str">
-        <v>Concept</v>
+        <v>Hands-on</v>
       </c>
       <c r="F63" t="str">
-        <v>Internal - incident history</v>
+        <v>docs.coveo.com - search: resource snapshots</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2820,19 +2820,19 @@
         <v>11. Configuration and useful APIs after go-live</v>
       </c>
       <c r="B64" t="str">
-        <v>Run and audit the configuration day to day, and know when to escalate.</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>Routine health checks</v>
+        <v>Admin and Search APIs worth knowing</v>
       </c>
       <c r="D64" t="str">
-        <v>Source health, indexed counts, failed runs, quota and consumption. What we check and how often.</v>
+        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
       </c>
       <c r="E64" t="str">
         <v>Hands-on</v>
       </c>
       <c r="F64" t="str">
-        <v>Internal - runbook</v>
+        <v>docs.coveo.com - search: platform API</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2861,16 +2861,16 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>Resource snapshots and promoting configuration</v>
+        <v>Monitoring and alerting</v>
       </c>
       <c r="D65" t="str">
-        <v>Capturing configuration, comparing organizations, and applying a snapshot.</v>
+        <v>What is monitored today, what triggers an alert, and who receives it.</v>
       </c>
       <c r="E65" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F65" t="str">
-        <v>docs.coveo.com - search: resource snapshots</v>
+        <v>Internal - monitoring</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2899,16 +2899,16 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>Admin and Search APIs worth knowing</v>
+        <v>Support and escalation</v>
       </c>
       <c r="D66" t="str">
-        <v>Endpoints we use for reporting, audits and bulk checks after go-live.</v>
+        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
       </c>
       <c r="E66" t="str">
-        <v>Hands-on</v>
+        <v>Concept</v>
       </c>
       <c r="F66" t="str">
-        <v>docs.coveo.com - search: platform API</v>
+        <v>Internal - escalation matrix</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2937,16 +2937,16 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>Monitoring and alerting</v>
+        <v>Documentation and ownership handover</v>
       </c>
       <c r="D67" t="str">
-        <v>What is monitored today, what triggers an alert, and who receives it.</v>
+        <v>What you own from here, where the runbook lives, and what you keep current.</v>
       </c>
       <c r="E67" t="str">
-        <v>Concept</v>
+        <v>Reading</v>
       </c>
       <c r="F67" t="str">
-        <v>Internal - monitoring</v>
+        <v>Internal - runbook</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2975,19 +2975,19 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>Support and escalation</v>
+        <v>Lead one indexing change end to end</v>
       </c>
       <c r="D68" t="str">
-        <v>Coveo support channels, what a useful ticket contains, and our internal escalation path.</v>
+        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
       </c>
       <c r="E68" t="str">
-        <v>Concept</v>
+        <v>Shadowing</v>
       </c>
       <c r="F68" t="str">
-        <v>Internal - escalation matrix</v>
+        <v>Internal</v>
       </c>
       <c r="G68" t="str">
-        <v/>
+        <v>The real exit criterion for this roadmap.</v>
       </c>
       <c r="H68" t="str">
         <v>No</v>
@@ -3002,88 +3002,12 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B69" t="str">
-        <v/>
-      </c>
-      <c r="C69" t="str">
-        <v>Documentation and ownership handover</v>
-      </c>
-      <c r="D69" t="str">
-        <v>What you own from here, where the runbook lives, and what you keep current.</v>
-      </c>
-      <c r="E69" t="str">
-        <v>Reading</v>
-      </c>
-      <c r="F69" t="str">
-        <v>Internal - runbook</v>
-      </c>
-      <c r="G69" t="str">
-        <v/>
-      </c>
-      <c r="H69" t="str">
-        <v>No</v>
-      </c>
-      <c r="I69" t="str">
-        <v/>
-      </c>
-      <c r="J69" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K69" t="str">
-        <v/>
-      </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>11. Configuration and useful APIs after go-live</v>
-      </c>
-      <c r="B70" t="str">
-        <v/>
-      </c>
-      <c r="C70" t="str">
-        <v>Lead one indexing change end to end</v>
-      </c>
-      <c r="D70" t="str">
-        <v>Plan it, validate on non-prod, apply to prod and report it, with me only observing.</v>
-      </c>
-      <c r="E70" t="str">
-        <v>Shadowing</v>
-      </c>
-      <c r="F70" t="str">
-        <v>Internal</v>
-      </c>
-      <c r="G70" t="str">
-        <v>The real exit criterion for this roadmap.</v>
-      </c>
-      <c r="H70" t="str">
-        <v>No</v>
-      </c>
-      <c r="I70" t="str">
-        <v/>
-      </c>
-      <c r="J70" t="str">
-        <v>Not started</v>
-      </c>
-      <c r="K70" t="str">
-        <v/>
-      </c>
-      <c r="L70" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L68"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/coveo-kt-tracker.xlsx
+++ b/coveo-kt-tracker.xlsx
@@ -3184,7 +3184,7 @@
         <v>Explaining</v>
       </c>
       <c r="B2" t="str">
-        <v>AKSHAY</v>
+        <v>Akshay</v>
       </c>
     </row>
     <row r="3">
@@ -3192,7 +3192,7 @@
         <v>Learning</v>
       </c>
       <c r="B3" t="str">
-        <v>DIVYASHREE</v>
+        <v>Divyashree</v>
       </c>
     </row>
   </sheetData>
